--- a/development/one_file_rosetta_output/SP125809_rosetta.xlsx
+++ b/development/one_file_rosetta_output/SP125809_rosetta.xlsx
@@ -398,14 +398,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:E452"/>
+  <dimension ref="A1:F452"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
     <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
     <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="70.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="70.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -426,10 +427,15 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
+          <t>N indels</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
           <t>Example n</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Indel in context</t>
         </is>
@@ -452,9 +458,12 @@
         </is>
       </c>
       <c r="D2" s="4">
+        <v>3</v>
+      </c>
+      <c r="E2" s="4">
         <v>1</v>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -508,9 +517,12 @@
         </is>
       </c>
       <c r="D3" s="4">
+        <v>3</v>
+      </c>
+      <c r="E3" s="4">
         <v>2</v>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -566,7 +578,10 @@
       <c r="D4" s="4">
         <v>3</v>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="4">
+        <v>3</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -622,7 +637,10 @@
       <c r="D5" s="4">
         <v>1</v>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="4">
+        <v>1</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -678,7 +696,10 @@
       <c r="D6" s="4">
         <v>1</v>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="4">
+        <v>1</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -741,7 +762,10 @@
       <c r="D7" s="4">
         <v>1</v>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="4">
+        <v>1</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -812,7 +836,10 @@
       <c r="D8" s="4">
         <v>1</v>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="4">
+        <v>1</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -840,7 +867,10 @@
       <c r="D9" s="4">
         <v>1</v>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="4">
+        <v>1</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -926,7 +956,10 @@
       <c r="D10" s="4">
         <v>1</v>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="4">
+        <v>1</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -954,7 +987,10 @@
       <c r="D11" s="4">
         <v>1</v>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="4">
+        <v>1</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1062,7 +1098,10 @@
       <c r="D12" s="4">
         <v>1</v>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="4">
+        <v>1</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1088,9 +1127,12 @@
         </is>
       </c>
       <c r="D13" s="4">
+        <v>2</v>
+      </c>
+      <c r="E13" s="4">
         <v>1</v>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1146,7 +1188,10 @@
       <c r="D14" s="4">
         <v>1</v>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="4">
+        <v>1</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1209,7 +1254,10 @@
       <c r="D15" s="4">
         <v>1</v>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="4">
+        <v>1</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1272,7 +1320,10 @@
       <c r="D16" s="4">
         <v>1</v>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="4">
+        <v>1</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1300,7 +1351,10 @@
       <c r="D17" s="4">
         <v>1</v>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="4">
+        <v>1</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1371,7 +1425,10 @@
       <c r="D18" s="4">
         <v>1</v>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="4">
+        <v>1</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1457,7 +1514,10 @@
       <c r="D19" s="4">
         <v>1</v>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="4">
+        <v>1</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1485,7 +1545,10 @@
       <c r="D20" s="4">
         <v>1</v>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="4">
+        <v>1</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1511,9 +1574,12 @@
         </is>
       </c>
       <c r="D21" s="4">
+        <v>2</v>
+      </c>
+      <c r="E21" s="4">
         <v>1</v>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1569,7 +1635,10 @@
       <c r="D22" s="4">
         <v>1</v>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E22" s="4">
+        <v>1</v>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1595,9 +1664,12 @@
         </is>
       </c>
       <c r="D23" s="4">
+        <v>2</v>
+      </c>
+      <c r="E23" s="4">
         <v>1</v>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1660,7 +1732,10 @@
       <c r="D24" s="4">
         <v>1</v>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E24" s="4">
+        <v>1</v>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1731,7 +1806,10 @@
       <c r="D25" s="4">
         <v>1</v>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E25" s="4">
+        <v>1</v>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1809,7 +1887,10 @@
       <c r="D26" s="4">
         <v>1</v>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E26" s="4">
+        <v>1</v>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1885,9 +1966,12 @@
         </is>
       </c>
       <c r="D27" s="4">
+        <v>2</v>
+      </c>
+      <c r="E27" s="4">
         <v>1</v>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1943,7 +2027,10 @@
       <c r="D28" s="4">
         <v>1</v>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E28" s="4">
+        <v>1</v>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1969,9 +2056,12 @@
         </is>
       </c>
       <c r="D29" s="4">
+        <v>2</v>
+      </c>
+      <c r="E29" s="4">
         <v>1</v>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1997,9 +2087,12 @@
         </is>
       </c>
       <c r="D30" s="4">
+        <v>4</v>
+      </c>
+      <c r="E30" s="4">
         <v>1</v>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2075,9 +2168,12 @@
         </is>
       </c>
       <c r="D31" s="4">
+        <v>4</v>
+      </c>
+      <c r="E31" s="4">
         <v>2</v>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2153,9 +2249,12 @@
         </is>
       </c>
       <c r="D32" s="4">
+        <v>3</v>
+      </c>
+      <c r="E32" s="4">
         <v>1</v>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2231,9 +2330,12 @@
         </is>
       </c>
       <c r="D33" s="4">
+        <v>3</v>
+      </c>
+      <c r="E33" s="4">
         <v>2</v>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2311,7 +2413,10 @@
       <c r="D34" s="4">
         <v>3</v>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="E34" s="4">
+        <v>3</v>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2387,9 +2492,12 @@
         </is>
       </c>
       <c r="D35" s="4">
+        <v>2</v>
+      </c>
+      <c r="E35" s="4">
         <v>1</v>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2415,9 +2523,12 @@
         </is>
       </c>
       <c r="D36" s="4">
+        <v>2</v>
+      </c>
+      <c r="E36" s="4">
         <v>1</v>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2503,7 +2614,10 @@
       <c r="D37" s="4">
         <v>1</v>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="E37" s="4">
+        <v>1</v>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2587,9 +2701,12 @@
         </is>
       </c>
       <c r="D38" s="4">
+        <v>3</v>
+      </c>
+      <c r="E38" s="4">
         <v>1</v>
       </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="F38" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2673,9 +2790,12 @@
         </is>
       </c>
       <c r="D39" s="4">
+        <v>3</v>
+      </c>
+      <c r="E39" s="4">
         <v>1</v>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2703,7 +2823,10 @@
       <c r="D40" s="4">
         <v>1</v>
       </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="E40" s="4">
+        <v>1</v>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2794,9 +2917,12 @@
         </is>
       </c>
       <c r="D41" s="4">
+        <v>4</v>
+      </c>
+      <c r="E41" s="4">
         <v>1</v>
       </c>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2887,9 +3013,12 @@
         </is>
       </c>
       <c r="D42" s="4">
+        <v>4</v>
+      </c>
+      <c r="E42" s="4">
         <v>2</v>
       </c>
-      <c r="E42" s="6" t="inlineStr">
+      <c r="F42" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2980,9 +3109,12 @@
         </is>
       </c>
       <c r="D43" s="4">
+        <v>3</v>
+      </c>
+      <c r="E43" s="4">
         <v>1</v>
       </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="F43" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3081,9 +3213,12 @@
         </is>
       </c>
       <c r="D44" s="4">
+        <v>3</v>
+      </c>
+      <c r="E44" s="4">
         <v>2</v>
       </c>
-      <c r="E44" s="6" t="inlineStr">
+      <c r="F44" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3182,9 +3317,12 @@
         </is>
       </c>
       <c r="D45" s="4">
+        <v>5</v>
+      </c>
+      <c r="E45" s="4">
         <v>1</v>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="F45" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3283,9 +3421,12 @@
         </is>
       </c>
       <c r="D46" s="4">
+        <v>5</v>
+      </c>
+      <c r="E46" s="4">
         <v>2</v>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="F46" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3384,9 +3525,12 @@
         </is>
       </c>
       <c r="D47" s="4">
+        <v>6</v>
+      </c>
+      <c r="E47" s="4">
         <v>1</v>
       </c>
-      <c r="E47" s="6" t="inlineStr">
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3485,9 +3629,12 @@
         </is>
       </c>
       <c r="D48" s="4">
+        <v>6</v>
+      </c>
+      <c r="E48" s="4">
         <v>2</v>
       </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="F48" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3586,9 +3733,12 @@
         </is>
       </c>
       <c r="D49" s="4">
+        <v>6</v>
+      </c>
+      <c r="E49" s="4">
         <v>3</v>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3687,9 +3837,12 @@
         </is>
       </c>
       <c r="D50" s="4">
+        <v>10</v>
+      </c>
+      <c r="E50" s="4">
         <v>1</v>
       </c>
-      <c r="E50" s="6" t="inlineStr">
+      <c r="F50" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3795,9 +3948,12 @@
         </is>
       </c>
       <c r="D51" s="4">
+        <v>10</v>
+      </c>
+      <c r="E51" s="4">
         <v>2</v>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="F51" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3903,9 +4059,12 @@
         </is>
       </c>
       <c r="D52" s="4">
+        <v>10</v>
+      </c>
+      <c r="E52" s="4">
         <v>3</v>
       </c>
-      <c r="E52" s="6" t="inlineStr">
+      <c r="F52" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4011,9 +4170,12 @@
         </is>
       </c>
       <c r="D53" s="4">
+        <v>10</v>
+      </c>
+      <c r="E53" s="4">
         <v>4</v>
       </c>
-      <c r="E53" s="6" t="inlineStr">
+      <c r="F53" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4119,9 +4281,12 @@
         </is>
       </c>
       <c r="D54" s="4">
+        <v>10</v>
+      </c>
+      <c r="E54" s="4">
         <v>5</v>
       </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="F54" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4227,9 +4392,12 @@
         </is>
       </c>
       <c r="D55" s="4">
+        <v>5</v>
+      </c>
+      <c r="E55" s="4">
         <v>1</v>
       </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="F55" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4335,9 +4503,12 @@
         </is>
       </c>
       <c r="D56" s="4">
+        <v>5</v>
+      </c>
+      <c r="E56" s="4">
         <v>2</v>
       </c>
-      <c r="E56" s="6" t="inlineStr">
+      <c r="F56" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4445,7 +4616,10 @@
       <c r="D57" s="4">
         <v>1</v>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="E57" s="4">
+        <v>1</v>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4551,9 +4725,12 @@
         </is>
       </c>
       <c r="D58" s="4">
+        <v>7</v>
+      </c>
+      <c r="E58" s="4">
         <v>1</v>
       </c>
-      <c r="E58" s="6" t="inlineStr">
+      <c r="F58" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4667,9 +4844,12 @@
         </is>
       </c>
       <c r="D59" s="4">
+        <v>3</v>
+      </c>
+      <c r="E59" s="4">
         <v>1</v>
       </c>
-      <c r="E59" s="6" t="inlineStr">
+      <c r="F59" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4783,9 +4963,12 @@
         </is>
       </c>
       <c r="D60" s="4">
+        <v>3</v>
+      </c>
+      <c r="E60" s="4">
         <v>2</v>
       </c>
-      <c r="E60" s="6" t="inlineStr">
+      <c r="F60" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4899,9 +5082,12 @@
         </is>
       </c>
       <c r="D61" s="4">
+        <v>5</v>
+      </c>
+      <c r="E61" s="4">
         <v>1</v>
       </c>
-      <c r="E61" s="6" t="inlineStr">
+      <c r="F61" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5015,9 +5201,12 @@
         </is>
       </c>
       <c r="D62" s="4">
+        <v>5</v>
+      </c>
+      <c r="E62" s="4">
         <v>2</v>
       </c>
-      <c r="E62" s="6" t="inlineStr">
+      <c r="F62" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5131,9 +5320,12 @@
         </is>
       </c>
       <c r="D63" s="4">
+        <v>5</v>
+      </c>
+      <c r="E63" s="4">
         <v>3</v>
       </c>
-      <c r="E63" s="6" t="inlineStr">
+      <c r="F63" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5249,7 +5441,10 @@
       <c r="D64" s="4">
         <v>1</v>
       </c>
-      <c r="E64" s="6" t="inlineStr">
+      <c r="E64" s="4">
+        <v>1</v>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5277,7 +5472,10 @@
       <c r="D65" s="4">
         <v>1</v>
       </c>
-      <c r="E65" s="6" t="inlineStr">
+      <c r="E65" s="4">
+        <v>1</v>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5305,7 +5503,10 @@
       <c r="D66" s="4">
         <v>1</v>
       </c>
-      <c r="E66" s="6" t="inlineStr">
+      <c r="E66" s="4">
+        <v>1</v>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5333,7 +5534,10 @@
       <c r="D67" s="4">
         <v>1</v>
       </c>
-      <c r="E67" s="6" t="inlineStr">
+      <c r="E67" s="4">
+        <v>1</v>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5396,7 +5600,10 @@
       <c r="D68" s="4">
         <v>1</v>
       </c>
-      <c r="E68" s="6" t="inlineStr">
+      <c r="E68" s="4">
+        <v>1</v>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5422,9 +5629,12 @@
         </is>
       </c>
       <c r="D69" s="4">
+        <v>3</v>
+      </c>
+      <c r="E69" s="4">
         <v>1</v>
       </c>
-      <c r="E69" s="6" t="inlineStr">
+      <c r="F69" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5508,9 +5718,12 @@
         </is>
       </c>
       <c r="D70" s="4">
+        <v>2</v>
+      </c>
+      <c r="E70" s="4">
         <v>1</v>
       </c>
-      <c r="E70" s="6" t="inlineStr">
+      <c r="F70" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5601,9 +5814,12 @@
         </is>
       </c>
       <c r="D71" s="4">
+        <v>2</v>
+      </c>
+      <c r="E71" s="4">
         <v>1</v>
       </c>
-      <c r="E71" s="6" t="inlineStr">
+      <c r="F71" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5696,7 +5912,10 @@
       <c r="D72" s="4">
         <v>1</v>
       </c>
-      <c r="E72" s="6" t="inlineStr">
+      <c r="E72" s="4">
+        <v>1</v>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5787,9 +6006,12 @@
         </is>
       </c>
       <c r="D73" s="4">
+        <v>3</v>
+      </c>
+      <c r="E73" s="4">
         <v>1</v>
       </c>
-      <c r="E73" s="6" t="inlineStr">
+      <c r="F73" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5888,9 +6110,12 @@
         </is>
       </c>
       <c r="D74" s="4">
+        <v>3</v>
+      </c>
+      <c r="E74" s="4">
         <v>2</v>
       </c>
-      <c r="E74" s="6" t="inlineStr">
+      <c r="F74" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5991,7 +6216,10 @@
       <c r="D75" s="4">
         <v>3</v>
       </c>
-      <c r="E75" s="6" t="inlineStr">
+      <c r="E75" s="4">
+        <v>3</v>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6090,9 +6318,12 @@
         </is>
       </c>
       <c r="D76" s="4">
+        <v>2</v>
+      </c>
+      <c r="E76" s="4">
         <v>1</v>
       </c>
-      <c r="E76" s="6" t="inlineStr">
+      <c r="F76" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6193,7 +6424,10 @@
       <c r="D77" s="4">
         <v>2</v>
       </c>
-      <c r="E77" s="6" t="inlineStr">
+      <c r="E77" s="4">
+        <v>2</v>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6292,9 +6526,12 @@
         </is>
       </c>
       <c r="D78" s="4">
+        <v>2</v>
+      </c>
+      <c r="E78" s="4">
         <v>1</v>
       </c>
-      <c r="E78" s="6" t="inlineStr">
+      <c r="F78" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6393,9 +6630,12 @@
         </is>
       </c>
       <c r="D79" s="4">
+        <v>9</v>
+      </c>
+      <c r="E79" s="4">
         <v>1</v>
       </c>
-      <c r="E79" s="6" t="inlineStr">
+      <c r="F79" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6501,9 +6741,12 @@
         </is>
       </c>
       <c r="D80" s="4">
+        <v>9</v>
+      </c>
+      <c r="E80" s="4">
         <v>2</v>
       </c>
-      <c r="E80" s="6" t="inlineStr">
+      <c r="F80" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6609,9 +6852,12 @@
         </is>
       </c>
       <c r="D81" s="4">
+        <v>9</v>
+      </c>
+      <c r="E81" s="4">
         <v>3</v>
       </c>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="F81" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6717,9 +6963,12 @@
         </is>
       </c>
       <c r="D82" s="4">
+        <v>9</v>
+      </c>
+      <c r="E82" s="4">
         <v>4</v>
       </c>
-      <c r="E82" s="6" t="inlineStr">
+      <c r="F82" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6825,9 +7074,12 @@
         </is>
       </c>
       <c r="D83" s="4">
+        <v>9</v>
+      </c>
+      <c r="E83" s="4">
         <v>5</v>
       </c>
-      <c r="E83" s="6" t="inlineStr">
+      <c r="F83" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6935,7 +7187,10 @@
       <c r="D84" s="4">
         <v>1</v>
       </c>
-      <c r="E84" s="6" t="inlineStr">
+      <c r="E84" s="4">
+        <v>1</v>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -6963,7 +7218,10 @@
       <c r="D85" s="4">
         <v>1</v>
       </c>
-      <c r="E85" s="6" t="inlineStr">
+      <c r="E85" s="4">
+        <v>1</v>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -6989,9 +7247,12 @@
         </is>
       </c>
       <c r="D86" s="4">
+        <v>5</v>
+      </c>
+      <c r="E86" s="4">
         <v>1</v>
       </c>
-      <c r="E86" s="6" t="inlineStr">
+      <c r="F86" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7105,9 +7366,12 @@
         </is>
       </c>
       <c r="D87" s="4">
+        <v>5</v>
+      </c>
+      <c r="E87" s="4">
         <v>2</v>
       </c>
-      <c r="E87" s="6" t="inlineStr">
+      <c r="F87" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7221,9 +7485,12 @@
         </is>
       </c>
       <c r="D88" s="4">
+        <v>6</v>
+      </c>
+      <c r="E88" s="4">
         <v>1</v>
       </c>
-      <c r="E88" s="6" t="inlineStr">
+      <c r="F88" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7337,9 +7604,12 @@
         </is>
       </c>
       <c r="D89" s="4">
+        <v>6</v>
+      </c>
+      <c r="E89" s="4">
         <v>2</v>
       </c>
-      <c r="E89" s="6" t="inlineStr">
+      <c r="F89" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7455,7 +7725,10 @@
       <c r="D90" s="4">
         <v>1</v>
       </c>
-      <c r="E90" s="6" t="inlineStr">
+      <c r="E90" s="4">
+        <v>1</v>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7571,7 +7844,10 @@
       <c r="D91" s="4">
         <v>1</v>
       </c>
-      <c r="E91" s="6" t="inlineStr">
+      <c r="E91" s="4">
+        <v>1</v>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7625,9 +7901,12 @@
         </is>
       </c>
       <c r="D92" s="4">
+        <v>2</v>
+      </c>
+      <c r="E92" s="4">
         <v>1</v>
       </c>
-      <c r="E92" s="6" t="inlineStr">
+      <c r="F92" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -7655,7 +7934,10 @@
       <c r="D93" s="4">
         <v>1</v>
       </c>
-      <c r="E93" s="6" t="inlineStr">
+      <c r="E93" s="4">
+        <v>1</v>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -7681,9 +7963,12 @@
         </is>
       </c>
       <c r="D94" s="4">
+        <v>2</v>
+      </c>
+      <c r="E94" s="4">
         <v>1</v>
       </c>
-      <c r="E94" s="6" t="inlineStr">
+      <c r="F94" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7754,7 +8039,10 @@
       <c r="D95" s="4">
         <v>2</v>
       </c>
-      <c r="E95" s="6" t="inlineStr">
+      <c r="E95" s="4">
+        <v>2</v>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7825,7 +8113,10 @@
       <c r="D96" s="4">
         <v>1</v>
       </c>
-      <c r="E96" s="6" t="inlineStr">
+      <c r="E96" s="4">
+        <v>1</v>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -7853,7 +8144,10 @@
       <c r="D97" s="4">
         <v>1</v>
       </c>
-      <c r="E97" s="6" t="inlineStr">
+      <c r="E97" s="4">
+        <v>1</v>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7931,7 +8225,10 @@
       <c r="D98" s="4">
         <v>1</v>
       </c>
-      <c r="E98" s="6" t="inlineStr">
+      <c r="E98" s="4">
+        <v>1</v>
+      </c>
+      <c r="F98" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -7957,9 +8254,12 @@
         </is>
       </c>
       <c r="D99" s="4">
+        <v>3</v>
+      </c>
+      <c r="E99" s="4">
         <v>1</v>
       </c>
-      <c r="E99" s="6" t="inlineStr">
+      <c r="F99" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8043,9 +8343,12 @@
         </is>
       </c>
       <c r="D100" s="4">
+        <v>3</v>
+      </c>
+      <c r="E100" s="4">
         <v>2</v>
       </c>
-      <c r="E100" s="6" t="inlineStr">
+      <c r="F100" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8129,9 +8432,12 @@
         </is>
       </c>
       <c r="D101" s="4">
+        <v>3</v>
+      </c>
+      <c r="E101" s="4">
         <v>1</v>
       </c>
-      <c r="E101" s="6" t="inlineStr">
+      <c r="F101" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8215,9 +8521,12 @@
         </is>
       </c>
       <c r="D102" s="4">
+        <v>3</v>
+      </c>
+      <c r="E102" s="4">
         <v>2</v>
       </c>
-      <c r="E102" s="6" t="inlineStr">
+      <c r="F102" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8303,7 +8612,10 @@
       <c r="D103" s="4">
         <v>3</v>
       </c>
-      <c r="E103" s="6" t="inlineStr">
+      <c r="E103" s="4">
+        <v>3</v>
+      </c>
+      <c r="F103" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8389,7 +8701,10 @@
       <c r="D104" s="4">
         <v>1</v>
       </c>
-      <c r="E104" s="6" t="inlineStr">
+      <c r="E104" s="4">
+        <v>1</v>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -8417,7 +8732,10 @@
       <c r="D105" s="4">
         <v>1</v>
       </c>
-      <c r="E105" s="6" t="inlineStr">
+      <c r="E105" s="4">
+        <v>1</v>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8516,9 +8834,12 @@
         </is>
       </c>
       <c r="D106" s="4">
+        <v>2</v>
+      </c>
+      <c r="E106" s="4">
         <v>1</v>
       </c>
-      <c r="E106" s="6" t="inlineStr">
+      <c r="F106" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8626,7 +8947,10 @@
       <c r="D107" s="4">
         <v>2</v>
       </c>
-      <c r="E107" s="6" t="inlineStr">
+      <c r="E107" s="4">
+        <v>2</v>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8734,7 +9058,10 @@
       <c r="D108" s="4">
         <v>1</v>
       </c>
-      <c r="E108" s="6" t="inlineStr">
+      <c r="E108" s="4">
+        <v>1</v>
+      </c>
+      <c r="F108" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -8760,9 +9087,12 @@
         </is>
       </c>
       <c r="D109" s="4">
+        <v>2</v>
+      </c>
+      <c r="E109" s="4">
         <v>1</v>
       </c>
-      <c r="E109" s="6" t="inlineStr">
+      <c r="F109" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -8788,9 +9118,12 @@
         </is>
       </c>
       <c r="D110" s="4">
+        <v>3</v>
+      </c>
+      <c r="E110" s="4">
         <v>1</v>
       </c>
-      <c r="E110" s="6" t="inlineStr">
+      <c r="F110" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8846,7 +9179,10 @@
       <c r="D111" s="4">
         <v>1</v>
       </c>
-      <c r="E111" s="6" t="inlineStr">
+      <c r="E111" s="4">
+        <v>1</v>
+      </c>
+      <c r="F111" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8932,7 +9268,10 @@
       <c r="D112" s="4">
         <v>1</v>
       </c>
-      <c r="E112" s="6" t="inlineStr">
+      <c r="E112" s="4">
+        <v>1</v>
+      </c>
+      <c r="F112" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9025,7 +9364,10 @@
       <c r="D113" s="4">
         <v>1</v>
       </c>
-      <c r="E113" s="6" t="inlineStr">
+      <c r="E113" s="4">
+        <v>1</v>
+      </c>
+      <c r="F113" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9116,9 +9458,12 @@
         </is>
       </c>
       <c r="D114" s="4">
+        <v>3</v>
+      </c>
+      <c r="E114" s="4">
         <v>1</v>
       </c>
-      <c r="E114" s="6" t="inlineStr">
+      <c r="F114" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9224,9 +9569,12 @@
         </is>
       </c>
       <c r="D115" s="4">
+        <v>3</v>
+      </c>
+      <c r="E115" s="4">
         <v>2</v>
       </c>
-      <c r="E115" s="6" t="inlineStr">
+      <c r="F115" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9332,9 +9680,12 @@
         </is>
       </c>
       <c r="D116" s="4">
+        <v>2</v>
+      </c>
+      <c r="E116" s="4">
         <v>1</v>
       </c>
-      <c r="E116" s="6" t="inlineStr">
+      <c r="F116" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9450,7 +9801,10 @@
       <c r="D117" s="4">
         <v>1</v>
       </c>
-      <c r="E117" s="6" t="inlineStr">
+      <c r="E117" s="4">
+        <v>1</v>
+      </c>
+      <c r="F117" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9549,9 +9903,12 @@
         </is>
       </c>
       <c r="D118" s="4">
+        <v>3</v>
+      </c>
+      <c r="E118" s="4">
         <v>1</v>
       </c>
-      <c r="E118" s="6" t="inlineStr">
+      <c r="F118" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9659,7 +10016,10 @@
       <c r="D119" s="4">
         <v>1</v>
       </c>
-      <c r="E119" s="6" t="inlineStr">
+      <c r="E119" s="4">
+        <v>1</v>
+      </c>
+      <c r="F119" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -9687,7 +10047,10 @@
       <c r="D120" s="4">
         <v>1</v>
       </c>
-      <c r="E120" s="6" t="inlineStr">
+      <c r="E120" s="4">
+        <v>1</v>
+      </c>
+      <c r="F120" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9803,7 +10166,10 @@
       <c r="D121" s="4">
         <v>1</v>
       </c>
-      <c r="E121" s="6" t="inlineStr">
+      <c r="E121" s="4">
+        <v>1</v>
+      </c>
+      <c r="F121" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -9829,9 +10195,12 @@
         </is>
       </c>
       <c r="D122" s="4">
+        <v>4</v>
+      </c>
+      <c r="E122" s="4">
         <v>1</v>
       </c>
-      <c r="E122" s="6" t="inlineStr">
+      <c r="F122" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9885,9 +10254,12 @@
         </is>
       </c>
       <c r="D123" s="4">
+        <v>4</v>
+      </c>
+      <c r="E123" s="4">
         <v>2</v>
       </c>
-      <c r="E123" s="6" t="inlineStr">
+      <c r="F123" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9943,7 +10315,10 @@
       <c r="D124" s="4">
         <v>1</v>
       </c>
-      <c r="E124" s="6" t="inlineStr">
+      <c r="E124" s="4">
+        <v>1</v>
+      </c>
+      <c r="F124" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -9969,9 +10344,12 @@
         </is>
       </c>
       <c r="D125" s="4">
+        <v>2</v>
+      </c>
+      <c r="E125" s="4">
         <v>1</v>
       </c>
-      <c r="E125" s="6" t="inlineStr">
+      <c r="F125" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10064,7 +10442,10 @@
       <c r="D126" s="4">
         <v>1</v>
       </c>
-      <c r="E126" s="6" t="inlineStr">
+      <c r="E126" s="4">
+        <v>1</v>
+      </c>
+      <c r="F126" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10157,7 +10538,10 @@
       <c r="D127" s="4">
         <v>1</v>
       </c>
-      <c r="E127" s="6" t="inlineStr">
+      <c r="E127" s="4">
+        <v>1</v>
+      </c>
+      <c r="F127" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -10185,7 +10569,10 @@
       <c r="D128" s="4">
         <v>1</v>
       </c>
-      <c r="E128" s="6" t="inlineStr">
+      <c r="E128" s="4">
+        <v>1</v>
+      </c>
+      <c r="F128" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10286,7 +10673,10 @@
       <c r="D129" s="4">
         <v>1</v>
       </c>
-      <c r="E129" s="6" t="inlineStr">
+      <c r="E129" s="4">
+        <v>1</v>
+      </c>
+      <c r="F129" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10400,9 +10790,12 @@
         </is>
       </c>
       <c r="D130" s="4">
+        <v>2</v>
+      </c>
+      <c r="E130" s="4">
         <v>1</v>
       </c>
-      <c r="E130" s="6" t="inlineStr">
+      <c r="F130" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10465,7 +10858,10 @@
       <c r="D131" s="4">
         <v>1</v>
       </c>
-      <c r="E131" s="6" t="inlineStr">
+      <c r="E131" s="4">
+        <v>1</v>
+      </c>
+      <c r="F131" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -10491,9 +10887,12 @@
         </is>
       </c>
       <c r="D132" s="4">
+        <v>5</v>
+      </c>
+      <c r="E132" s="4">
         <v>1</v>
       </c>
-      <c r="E132" s="6" t="inlineStr">
+      <c r="F132" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10569,9 +10968,12 @@
         </is>
       </c>
       <c r="D133" s="4">
+        <v>5</v>
+      </c>
+      <c r="E133" s="4">
         <v>2</v>
       </c>
-      <c r="E133" s="6" t="inlineStr">
+      <c r="F133" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10649,7 +11051,10 @@
       <c r="D134" s="4">
         <v>1</v>
       </c>
-      <c r="E134" s="6" t="inlineStr">
+      <c r="E134" s="4">
+        <v>1</v>
+      </c>
+      <c r="F134" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10725,9 +11130,12 @@
         </is>
       </c>
       <c r="D135" s="4">
+        <v>4</v>
+      </c>
+      <c r="E135" s="4">
         <v>1</v>
       </c>
-      <c r="E135" s="6" t="inlineStr">
+      <c r="F135" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10811,9 +11219,12 @@
         </is>
       </c>
       <c r="D136" s="4">
+        <v>3</v>
+      </c>
+      <c r="E136" s="4">
         <v>1</v>
       </c>
-      <c r="E136" s="6" t="inlineStr">
+      <c r="F136" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10897,9 +11308,12 @@
         </is>
       </c>
       <c r="D137" s="4">
+        <v>3</v>
+      </c>
+      <c r="E137" s="4">
         <v>2</v>
       </c>
-      <c r="E137" s="6" t="inlineStr">
+      <c r="F137" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10983,9 +11397,12 @@
         </is>
       </c>
       <c r="D138" s="4">
+        <v>3</v>
+      </c>
+      <c r="E138" s="4">
         <v>1</v>
       </c>
-      <c r="E138" s="6" t="inlineStr">
+      <c r="F138" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11069,9 +11486,12 @@
         </is>
       </c>
       <c r="D139" s="4">
+        <v>3</v>
+      </c>
+      <c r="E139" s="4">
         <v>2</v>
       </c>
-      <c r="E139" s="6" t="inlineStr">
+      <c r="F139" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11155,9 +11575,12 @@
         </is>
       </c>
       <c r="D140" s="4">
+        <v>8</v>
+      </c>
+      <c r="E140" s="4">
         <v>1</v>
       </c>
-      <c r="E140" s="6" t="inlineStr">
+      <c r="F140" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11248,9 +11671,12 @@
         </is>
       </c>
       <c r="D141" s="4">
+        <v>8</v>
+      </c>
+      <c r="E141" s="4">
         <v>2</v>
       </c>
-      <c r="E141" s="6" t="inlineStr">
+      <c r="F141" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11341,9 +11767,12 @@
         </is>
       </c>
       <c r="D142" s="4">
+        <v>8</v>
+      </c>
+      <c r="E142" s="4">
         <v>1</v>
       </c>
-      <c r="E142" s="6" t="inlineStr">
+      <c r="F142" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11434,9 +11863,12 @@
         </is>
       </c>
       <c r="D143" s="4">
+        <v>8</v>
+      </c>
+      <c r="E143" s="4">
         <v>2</v>
       </c>
-      <c r="E143" s="6" t="inlineStr">
+      <c r="F143" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11527,9 +11959,12 @@
         </is>
       </c>
       <c r="D144" s="4">
+        <v>8</v>
+      </c>
+      <c r="E144" s="4">
         <v>3</v>
       </c>
-      <c r="E144" s="6" t="inlineStr">
+      <c r="F144" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11620,9 +12055,12 @@
         </is>
       </c>
       <c r="D145" s="4">
+        <v>8</v>
+      </c>
+      <c r="E145" s="4">
         <v>4</v>
       </c>
-      <c r="E145" s="6" t="inlineStr">
+      <c r="F145" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11713,9 +12151,12 @@
         </is>
       </c>
       <c r="D146" s="4">
+        <v>8</v>
+      </c>
+      <c r="E146" s="4">
         <v>5</v>
       </c>
-      <c r="E146" s="6" t="inlineStr">
+      <c r="F146" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11806,9 +12247,12 @@
         </is>
       </c>
       <c r="D147" s="4">
+        <v>8</v>
+      </c>
+      <c r="E147" s="4">
         <v>1</v>
       </c>
-      <c r="E147" s="6" t="inlineStr">
+      <c r="F147" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11899,9 +12343,12 @@
         </is>
       </c>
       <c r="D148" s="4">
+        <v>8</v>
+      </c>
+      <c r="E148" s="4">
         <v>2</v>
       </c>
-      <c r="E148" s="6" t="inlineStr">
+      <c r="F148" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11992,9 +12439,12 @@
         </is>
       </c>
       <c r="D149" s="4">
+        <v>8</v>
+      </c>
+      <c r="E149" s="4">
         <v>3</v>
       </c>
-      <c r="E149" s="6" t="inlineStr">
+      <c r="F149" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12085,9 +12535,12 @@
         </is>
       </c>
       <c r="D150" s="4">
+        <v>8</v>
+      </c>
+      <c r="E150" s="4">
         <v>4</v>
       </c>
-      <c r="E150" s="6" t="inlineStr">
+      <c r="F150" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12178,9 +12631,12 @@
         </is>
       </c>
       <c r="D151" s="4">
+        <v>8</v>
+      </c>
+      <c r="E151" s="4">
         <v>5</v>
       </c>
-      <c r="E151" s="6" t="inlineStr">
+      <c r="F151" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12271,9 +12727,12 @@
         </is>
       </c>
       <c r="D152" s="4">
+        <v>16</v>
+      </c>
+      <c r="E152" s="4">
         <v>1</v>
       </c>
-      <c r="E152" s="6" t="inlineStr">
+      <c r="F152" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12372,9 +12831,12 @@
         </is>
       </c>
       <c r="D153" s="4">
+        <v>16</v>
+      </c>
+      <c r="E153" s="4">
         <v>2</v>
       </c>
-      <c r="E153" s="6" t="inlineStr">
+      <c r="F153" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12473,9 +12935,12 @@
         </is>
       </c>
       <c r="D154" s="4">
+        <v>16</v>
+      </c>
+      <c r="E154" s="4">
         <v>3</v>
       </c>
-      <c r="E154" s="6" t="inlineStr">
+      <c r="F154" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12574,9 +13039,12 @@
         </is>
       </c>
       <c r="D155" s="4">
+        <v>16</v>
+      </c>
+      <c r="E155" s="4">
         <v>4</v>
       </c>
-      <c r="E155" s="6" t="inlineStr">
+      <c r="F155" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12675,9 +13143,12 @@
         </is>
       </c>
       <c r="D156" s="4">
+        <v>16</v>
+      </c>
+      <c r="E156" s="4">
         <v>5</v>
       </c>
-      <c r="E156" s="6" t="inlineStr">
+      <c r="F156" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12776,9 +13247,12 @@
         </is>
       </c>
       <c r="D157" s="4">
+        <v>22</v>
+      </c>
+      <c r="E157" s="4">
         <v>1</v>
       </c>
-      <c r="E157" s="6" t="inlineStr">
+      <c r="F157" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12877,9 +13351,12 @@
         </is>
       </c>
       <c r="D158" s="4">
+        <v>22</v>
+      </c>
+      <c r="E158" s="4">
         <v>2</v>
       </c>
-      <c r="E158" s="6" t="inlineStr">
+      <c r="F158" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12978,9 +13455,12 @@
         </is>
       </c>
       <c r="D159" s="4">
+        <v>22</v>
+      </c>
+      <c r="E159" s="4">
         <v>3</v>
       </c>
-      <c r="E159" s="6" t="inlineStr">
+      <c r="F159" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13079,9 +13559,12 @@
         </is>
       </c>
       <c r="D160" s="4">
+        <v>22</v>
+      </c>
+      <c r="E160" s="4">
         <v>4</v>
       </c>
-      <c r="E160" s="6" t="inlineStr">
+      <c r="F160" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13180,9 +13663,12 @@
         </is>
       </c>
       <c r="D161" s="4">
+        <v>22</v>
+      </c>
+      <c r="E161" s="4">
         <v>5</v>
       </c>
-      <c r="E161" s="6" t="inlineStr">
+      <c r="F161" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13281,9 +13767,12 @@
         </is>
       </c>
       <c r="D162" s="4">
+        <v>23</v>
+      </c>
+      <c r="E162" s="4">
         <v>1</v>
       </c>
-      <c r="E162" s="6" t="inlineStr">
+      <c r="F162" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13382,9 +13871,12 @@
         </is>
       </c>
       <c r="D163" s="4">
+        <v>23</v>
+      </c>
+      <c r="E163" s="4">
         <v>2</v>
       </c>
-      <c r="E163" s="6" t="inlineStr">
+      <c r="F163" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13483,9 +13975,12 @@
         </is>
       </c>
       <c r="D164" s="4">
+        <v>23</v>
+      </c>
+      <c r="E164" s="4">
         <v>3</v>
       </c>
-      <c r="E164" s="6" t="inlineStr">
+      <c r="F164" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13584,9 +14079,12 @@
         </is>
       </c>
       <c r="D165" s="4">
+        <v>23</v>
+      </c>
+      <c r="E165" s="4">
         <v>4</v>
       </c>
-      <c r="E165" s="6" t="inlineStr">
+      <c r="F165" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13685,9 +14183,12 @@
         </is>
       </c>
       <c r="D166" s="4">
+        <v>23</v>
+      </c>
+      <c r="E166" s="4">
         <v>5</v>
       </c>
-      <c r="E166" s="6" t="inlineStr">
+      <c r="F166" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13786,9 +14287,12 @@
         </is>
       </c>
       <c r="D167" s="4">
+        <v>17</v>
+      </c>
+      <c r="E167" s="4">
         <v>1</v>
       </c>
-      <c r="E167" s="6" t="inlineStr">
+      <c r="F167" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13894,9 +14398,12 @@
         </is>
       </c>
       <c r="D168" s="4">
+        <v>17</v>
+      </c>
+      <c r="E168" s="4">
         <v>2</v>
       </c>
-      <c r="E168" s="6" t="inlineStr">
+      <c r="F168" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14002,9 +14509,12 @@
         </is>
       </c>
       <c r="D169" s="4">
+        <v>17</v>
+      </c>
+      <c r="E169" s="4">
         <v>3</v>
       </c>
-      <c r="E169" s="6" t="inlineStr">
+      <c r="F169" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14110,9 +14620,12 @@
         </is>
       </c>
       <c r="D170" s="4">
+        <v>17</v>
+      </c>
+      <c r="E170" s="4">
         <v>4</v>
       </c>
-      <c r="E170" s="6" t="inlineStr">
+      <c r="F170" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14218,9 +14731,12 @@
         </is>
       </c>
       <c r="D171" s="4">
+        <v>17</v>
+      </c>
+      <c r="E171" s="4">
         <v>5</v>
       </c>
-      <c r="E171" s="6" t="inlineStr">
+      <c r="F171" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14326,9 +14842,12 @@
         </is>
       </c>
       <c r="D172" s="4">
+        <v>12</v>
+      </c>
+      <c r="E172" s="4">
         <v>1</v>
       </c>
-      <c r="E172" s="6" t="inlineStr">
+      <c r="F172" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14434,9 +14953,12 @@
         </is>
       </c>
       <c r="D173" s="4">
+        <v>12</v>
+      </c>
+      <c r="E173" s="4">
         <v>2</v>
       </c>
-      <c r="E173" s="6" t="inlineStr">
+      <c r="F173" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14542,9 +15064,12 @@
         </is>
       </c>
       <c r="D174" s="4">
+        <v>12</v>
+      </c>
+      <c r="E174" s="4">
         <v>3</v>
       </c>
-      <c r="E174" s="6" t="inlineStr">
+      <c r="F174" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14650,9 +15175,12 @@
         </is>
       </c>
       <c r="D175" s="4">
+        <v>12</v>
+      </c>
+      <c r="E175" s="4">
         <v>4</v>
       </c>
-      <c r="E175" s="6" t="inlineStr">
+      <c r="F175" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14758,9 +15286,12 @@
         </is>
       </c>
       <c r="D176" s="4">
+        <v>12</v>
+      </c>
+      <c r="E176" s="4">
         <v>5</v>
       </c>
-      <c r="E176" s="6" t="inlineStr">
+      <c r="F176" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14866,9 +15397,12 @@
         </is>
       </c>
       <c r="D177" s="4">
+        <v>19</v>
+      </c>
+      <c r="E177" s="4">
         <v>1</v>
       </c>
-      <c r="E177" s="6" t="inlineStr">
+      <c r="F177" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14974,9 +15508,12 @@
         </is>
       </c>
       <c r="D178" s="4">
+        <v>19</v>
+      </c>
+      <c r="E178" s="4">
         <v>2</v>
       </c>
-      <c r="E178" s="6" t="inlineStr">
+      <c r="F178" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15082,9 +15619,12 @@
         </is>
       </c>
       <c r="D179" s="4">
+        <v>19</v>
+      </c>
+      <c r="E179" s="4">
         <v>3</v>
       </c>
-      <c r="E179" s="6" t="inlineStr">
+      <c r="F179" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15190,9 +15730,12 @@
         </is>
       </c>
       <c r="D180" s="4">
+        <v>19</v>
+      </c>
+      <c r="E180" s="4">
         <v>4</v>
       </c>
-      <c r="E180" s="6" t="inlineStr">
+      <c r="F180" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15298,9 +15841,12 @@
         </is>
       </c>
       <c r="D181" s="4">
+        <v>19</v>
+      </c>
+      <c r="E181" s="4">
         <v>5</v>
       </c>
-      <c r="E181" s="6" t="inlineStr">
+      <c r="F181" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15406,9 +15952,12 @@
         </is>
       </c>
       <c r="D182" s="4">
+        <v>24</v>
+      </c>
+      <c r="E182" s="4">
         <v>1</v>
       </c>
-      <c r="E182" s="6" t="inlineStr">
+      <c r="F182" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15522,9 +16071,12 @@
         </is>
       </c>
       <c r="D183" s="4">
+        <v>24</v>
+      </c>
+      <c r="E183" s="4">
         <v>2</v>
       </c>
-      <c r="E183" s="6" t="inlineStr">
+      <c r="F183" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15638,9 +16190,12 @@
         </is>
       </c>
       <c r="D184" s="4">
+        <v>24</v>
+      </c>
+      <c r="E184" s="4">
         <v>3</v>
       </c>
-      <c r="E184" s="6" t="inlineStr">
+      <c r="F184" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15754,9 +16309,12 @@
         </is>
       </c>
       <c r="D185" s="4">
+        <v>24</v>
+      </c>
+      <c r="E185" s="4">
         <v>4</v>
       </c>
-      <c r="E185" s="6" t="inlineStr">
+      <c r="F185" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15870,9 +16428,12 @@
         </is>
       </c>
       <c r="D186" s="4">
+        <v>24</v>
+      </c>
+      <c r="E186" s="4">
         <v>5</v>
       </c>
-      <c r="E186" s="6" t="inlineStr">
+      <c r="F186" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15986,9 +16547,12 @@
         </is>
       </c>
       <c r="D187" s="4">
+        <v>14</v>
+      </c>
+      <c r="E187" s="4">
         <v>1</v>
       </c>
-      <c r="E187" s="6" t="inlineStr">
+      <c r="F187" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16102,9 +16666,12 @@
         </is>
       </c>
       <c r="D188" s="4">
+        <v>14</v>
+      </c>
+      <c r="E188" s="4">
         <v>2</v>
       </c>
-      <c r="E188" s="6" t="inlineStr">
+      <c r="F188" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16218,9 +16785,12 @@
         </is>
       </c>
       <c r="D189" s="4">
+        <v>14</v>
+      </c>
+      <c r="E189" s="4">
         <v>3</v>
       </c>
-      <c r="E189" s="6" t="inlineStr">
+      <c r="F189" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16334,9 +16904,12 @@
         </is>
       </c>
       <c r="D190" s="4">
+        <v>14</v>
+      </c>
+      <c r="E190" s="4">
         <v>4</v>
       </c>
-      <c r="E190" s="6" t="inlineStr">
+      <c r="F190" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16450,9 +17023,12 @@
         </is>
       </c>
       <c r="D191" s="4">
+        <v>14</v>
+      </c>
+      <c r="E191" s="4">
         <v>5</v>
       </c>
-      <c r="E191" s="6" t="inlineStr">
+      <c r="F191" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16566,9 +17142,12 @@
         </is>
       </c>
       <c r="D192" s="4">
+        <v>17</v>
+      </c>
+      <c r="E192" s="4">
         <v>1</v>
       </c>
-      <c r="E192" s="6" t="inlineStr">
+      <c r="F192" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16682,9 +17261,12 @@
         </is>
       </c>
       <c r="D193" s="4">
+        <v>17</v>
+      </c>
+      <c r="E193" s="4">
         <v>2</v>
       </c>
-      <c r="E193" s="6" t="inlineStr">
+      <c r="F193" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16798,9 +17380,12 @@
         </is>
       </c>
       <c r="D194" s="4">
+        <v>17</v>
+      </c>
+      <c r="E194" s="4">
         <v>3</v>
       </c>
-      <c r="E194" s="6" t="inlineStr">
+      <c r="F194" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16914,9 +17499,12 @@
         </is>
       </c>
       <c r="D195" s="4">
+        <v>17</v>
+      </c>
+      <c r="E195" s="4">
         <v>4</v>
       </c>
-      <c r="E195" s="6" t="inlineStr">
+      <c r="F195" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17030,9 +17618,12 @@
         </is>
       </c>
       <c r="D196" s="4">
+        <v>17</v>
+      </c>
+      <c r="E196" s="4">
         <v>5</v>
       </c>
-      <c r="E196" s="6" t="inlineStr">
+      <c r="F196" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17146,9 +17737,12 @@
         </is>
       </c>
       <c r="D197" s="4">
+        <v>10</v>
+      </c>
+      <c r="E197" s="4">
         <v>1</v>
       </c>
-      <c r="E197" s="6" t="inlineStr">
+      <c r="F197" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17269,9 +17863,12 @@
         </is>
       </c>
       <c r="D198" s="4">
+        <v>10</v>
+      </c>
+      <c r="E198" s="4">
         <v>2</v>
       </c>
-      <c r="E198" s="6" t="inlineStr">
+      <c r="F198" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17392,9 +17989,12 @@
         </is>
       </c>
       <c r="D199" s="4">
+        <v>7</v>
+      </c>
+      <c r="E199" s="4">
         <v>1</v>
       </c>
-      <c r="E199" s="6" t="inlineStr">
+      <c r="F199" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17515,9 +18115,12 @@
         </is>
       </c>
       <c r="D200" s="4">
+        <v>7</v>
+      </c>
+      <c r="E200" s="4">
         <v>2</v>
       </c>
-      <c r="E200" s="6" t="inlineStr">
+      <c r="F200" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17638,9 +18241,12 @@
         </is>
       </c>
       <c r="D201" s="4">
+        <v>7</v>
+      </c>
+      <c r="E201" s="4">
         <v>3</v>
       </c>
-      <c r="E201" s="6" t="inlineStr">
+      <c r="F201" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17761,9 +18367,12 @@
         </is>
       </c>
       <c r="D202" s="4">
+        <v>2</v>
+      </c>
+      <c r="E202" s="4">
         <v>1</v>
       </c>
-      <c r="E202" s="6" t="inlineStr">
+      <c r="F202" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17886,7 +18495,10 @@
       <c r="D203" s="4">
         <v>1</v>
       </c>
-      <c r="E203" s="6" t="inlineStr">
+      <c r="E203" s="4">
+        <v>1</v>
+      </c>
+      <c r="F203" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -17914,7 +18526,10 @@
       <c r="D204" s="4">
         <v>1</v>
       </c>
-      <c r="E204" s="6" t="inlineStr">
+      <c r="E204" s="4">
+        <v>1</v>
+      </c>
+      <c r="F204" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17983,9 +18598,12 @@
         </is>
       </c>
       <c r="D205" s="4">
+        <v>3</v>
+      </c>
+      <c r="E205" s="4">
         <v>1</v>
       </c>
-      <c r="E205" s="6" t="inlineStr">
+      <c r="F205" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18061,9 +18679,12 @@
         </is>
       </c>
       <c r="D206" s="4">
+        <v>2</v>
+      </c>
+      <c r="E206" s="4">
         <v>1</v>
       </c>
-      <c r="E206" s="6" t="inlineStr">
+      <c r="F206" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18141,7 +18762,10 @@
       <c r="D207" s="4">
         <v>2</v>
       </c>
-      <c r="E207" s="6" t="inlineStr">
+      <c r="E207" s="4">
+        <v>2</v>
+      </c>
+      <c r="F207" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18219,7 +18843,10 @@
       <c r="D208" s="4">
         <v>1</v>
       </c>
-      <c r="E208" s="6" t="inlineStr">
+      <c r="E208" s="4">
+        <v>1</v>
+      </c>
+      <c r="F208" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18305,7 +18932,10 @@
       <c r="D209" s="4">
         <v>1</v>
       </c>
-      <c r="E209" s="6" t="inlineStr">
+      <c r="E209" s="4">
+        <v>1</v>
+      </c>
+      <c r="F209" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18389,9 +19019,12 @@
         </is>
       </c>
       <c r="D210" s="4">
+        <v>3</v>
+      </c>
+      <c r="E210" s="4">
         <v>1</v>
       </c>
-      <c r="E210" s="6" t="inlineStr">
+      <c r="F210" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18482,9 +19115,12 @@
         </is>
       </c>
       <c r="D211" s="4">
+        <v>3</v>
+      </c>
+      <c r="E211" s="4">
         <v>1</v>
       </c>
-      <c r="E211" s="6" t="inlineStr">
+      <c r="F211" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18575,9 +19211,12 @@
         </is>
       </c>
       <c r="D212" s="4">
+        <v>3</v>
+      </c>
+      <c r="E212" s="4">
         <v>2</v>
       </c>
-      <c r="E212" s="6" t="inlineStr">
+      <c r="F212" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18668,9 +19307,12 @@
         </is>
       </c>
       <c r="D213" s="4">
+        <v>8</v>
+      </c>
+      <c r="E213" s="4">
         <v>1</v>
       </c>
-      <c r="E213" s="6" t="inlineStr">
+      <c r="F213" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18769,9 +19411,12 @@
         </is>
       </c>
       <c r="D214" s="4">
+        <v>8</v>
+      </c>
+      <c r="E214" s="4">
         <v>2</v>
       </c>
-      <c r="E214" s="6" t="inlineStr">
+      <c r="F214" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18870,9 +19515,12 @@
         </is>
       </c>
       <c r="D215" s="4">
+        <v>8</v>
+      </c>
+      <c r="E215" s="4">
         <v>3</v>
       </c>
-      <c r="E215" s="6" t="inlineStr">
+      <c r="F215" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18971,9 +19619,12 @@
         </is>
       </c>
       <c r="D216" s="4">
+        <v>8</v>
+      </c>
+      <c r="E216" s="4">
         <v>4</v>
       </c>
-      <c r="E216" s="6" t="inlineStr">
+      <c r="F216" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19072,9 +19723,12 @@
         </is>
       </c>
       <c r="D217" s="4">
+        <v>8</v>
+      </c>
+      <c r="E217" s="4">
         <v>5</v>
       </c>
-      <c r="E217" s="6" t="inlineStr">
+      <c r="F217" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19173,9 +19827,12 @@
         </is>
       </c>
       <c r="D218" s="4">
+        <v>16</v>
+      </c>
+      <c r="E218" s="4">
         <v>1</v>
       </c>
-      <c r="E218" s="6" t="inlineStr">
+      <c r="F218" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19274,9 +19931,12 @@
         </is>
       </c>
       <c r="D219" s="4">
+        <v>16</v>
+      </c>
+      <c r="E219" s="4">
         <v>2</v>
       </c>
-      <c r="E219" s="6" t="inlineStr">
+      <c r="F219" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19375,9 +20035,12 @@
         </is>
       </c>
       <c r="D220" s="4">
+        <v>16</v>
+      </c>
+      <c r="E220" s="4">
         <v>3</v>
       </c>
-      <c r="E220" s="6" t="inlineStr">
+      <c r="F220" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19476,9 +20139,12 @@
         </is>
       </c>
       <c r="D221" s="4">
+        <v>16</v>
+      </c>
+      <c r="E221" s="4">
         <v>4</v>
       </c>
-      <c r="E221" s="6" t="inlineStr">
+      <c r="F221" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19577,9 +20243,12 @@
         </is>
       </c>
       <c r="D222" s="4">
+        <v>16</v>
+      </c>
+      <c r="E222" s="4">
         <v>5</v>
       </c>
-      <c r="E222" s="6" t="inlineStr">
+      <c r="F222" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19678,9 +20347,12 @@
         </is>
       </c>
       <c r="D223" s="4">
+        <v>16</v>
+      </c>
+      <c r="E223" s="4">
         <v>1</v>
       </c>
-      <c r="E223" s="6" t="inlineStr">
+      <c r="F223" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19779,9 +20451,12 @@
         </is>
       </c>
       <c r="D224" s="4">
+        <v>16</v>
+      </c>
+      <c r="E224" s="4">
         <v>2</v>
       </c>
-      <c r="E224" s="6" t="inlineStr">
+      <c r="F224" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19880,9 +20555,12 @@
         </is>
       </c>
       <c r="D225" s="4">
+        <v>16</v>
+      </c>
+      <c r="E225" s="4">
         <v>3</v>
       </c>
-      <c r="E225" s="6" t="inlineStr">
+      <c r="F225" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19981,9 +20659,12 @@
         </is>
       </c>
       <c r="D226" s="4">
+        <v>16</v>
+      </c>
+      <c r="E226" s="4">
         <v>4</v>
       </c>
-      <c r="E226" s="6" t="inlineStr">
+      <c r="F226" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20082,9 +20763,12 @@
         </is>
       </c>
       <c r="D227" s="4">
+        <v>16</v>
+      </c>
+      <c r="E227" s="4">
         <v>5</v>
       </c>
-      <c r="E227" s="6" t="inlineStr">
+      <c r="F227" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20183,9 +20867,12 @@
         </is>
       </c>
       <c r="D228" s="4">
+        <v>10</v>
+      </c>
+      <c r="E228" s="4">
         <v>1</v>
       </c>
-      <c r="E228" s="6" t="inlineStr">
+      <c r="F228" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20291,9 +20978,12 @@
         </is>
       </c>
       <c r="D229" s="4">
+        <v>10</v>
+      </c>
+      <c r="E229" s="4">
         <v>2</v>
       </c>
-      <c r="E229" s="6" t="inlineStr">
+      <c r="F229" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20399,9 +21089,12 @@
         </is>
       </c>
       <c r="D230" s="4">
+        <v>10</v>
+      </c>
+      <c r="E230" s="4">
         <v>3</v>
       </c>
-      <c r="E230" s="6" t="inlineStr">
+      <c r="F230" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20507,9 +21200,12 @@
         </is>
       </c>
       <c r="D231" s="4">
+        <v>10</v>
+      </c>
+      <c r="E231" s="4">
         <v>4</v>
       </c>
-      <c r="E231" s="6" t="inlineStr">
+      <c r="F231" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20615,9 +21311,12 @@
         </is>
       </c>
       <c r="D232" s="4">
+        <v>6</v>
+      </c>
+      <c r="E232" s="4">
         <v>1</v>
       </c>
-      <c r="E232" s="6" t="inlineStr">
+      <c r="F232" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20723,9 +21422,12 @@
         </is>
       </c>
       <c r="D233" s="4">
+        <v>6</v>
+      </c>
+      <c r="E233" s="4">
         <v>2</v>
       </c>
-      <c r="E233" s="6" t="inlineStr">
+      <c r="F233" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20831,9 +21533,12 @@
         </is>
       </c>
       <c r="D234" s="4">
+        <v>6</v>
+      </c>
+      <c r="E234" s="4">
         <v>3</v>
       </c>
-      <c r="E234" s="6" t="inlineStr">
+      <c r="F234" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20939,9 +21644,12 @@
         </is>
       </c>
       <c r="D235" s="4">
+        <v>6</v>
+      </c>
+      <c r="E235" s="4">
         <v>4</v>
       </c>
-      <c r="E235" s="6" t="inlineStr">
+      <c r="F235" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21047,9 +21755,12 @@
         </is>
       </c>
       <c r="D236" s="4">
+        <v>11</v>
+      </c>
+      <c r="E236" s="4">
         <v>1</v>
       </c>
-      <c r="E236" s="6" t="inlineStr">
+      <c r="F236" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21155,9 +21866,12 @@
         </is>
       </c>
       <c r="D237" s="4">
+        <v>11</v>
+      </c>
+      <c r="E237" s="4">
         <v>2</v>
       </c>
-      <c r="E237" s="6" t="inlineStr">
+      <c r="F237" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21263,9 +21977,12 @@
         </is>
       </c>
       <c r="D238" s="4">
+        <v>11</v>
+      </c>
+      <c r="E238" s="4">
         <v>3</v>
       </c>
-      <c r="E238" s="6" t="inlineStr">
+      <c r="F238" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21371,9 +22088,12 @@
         </is>
       </c>
       <c r="D239" s="4">
+        <v>11</v>
+      </c>
+      <c r="E239" s="4">
         <v>4</v>
       </c>
-      <c r="E239" s="6" t="inlineStr">
+      <c r="F239" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21479,9 +22199,12 @@
         </is>
       </c>
       <c r="D240" s="4">
+        <v>11</v>
+      </c>
+      <c r="E240" s="4">
         <v>5</v>
       </c>
-      <c r="E240" s="6" t="inlineStr">
+      <c r="F240" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21587,9 +22310,12 @@
         </is>
       </c>
       <c r="D241" s="4">
+        <v>11</v>
+      </c>
+      <c r="E241" s="4">
         <v>1</v>
       </c>
-      <c r="E241" s="6" t="inlineStr">
+      <c r="F241" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21703,9 +22429,12 @@
         </is>
       </c>
       <c r="D242" s="4">
+        <v>11</v>
+      </c>
+      <c r="E242" s="4">
         <v>2</v>
       </c>
-      <c r="E242" s="6" t="inlineStr">
+      <c r="F242" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21819,9 +22548,12 @@
         </is>
       </c>
       <c r="D243" s="4">
+        <v>11</v>
+      </c>
+      <c r="E243" s="4">
         <v>3</v>
       </c>
-      <c r="E243" s="6" t="inlineStr">
+      <c r="F243" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21935,9 +22667,12 @@
         </is>
       </c>
       <c r="D244" s="4">
+        <v>11</v>
+      </c>
+      <c r="E244" s="4">
         <v>4</v>
       </c>
-      <c r="E244" s="6" t="inlineStr">
+      <c r="F244" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22051,9 +22786,12 @@
         </is>
       </c>
       <c r="D245" s="4">
+        <v>11</v>
+      </c>
+      <c r="E245" s="4">
         <v>5</v>
       </c>
-      <c r="E245" s="6" t="inlineStr">
+      <c r="F245" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22167,9 +22905,12 @@
         </is>
       </c>
       <c r="D246" s="4">
+        <v>12</v>
+      </c>
+      <c r="E246" s="4">
         <v>1</v>
       </c>
-      <c r="E246" s="6" t="inlineStr">
+      <c r="F246" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22283,9 +23024,12 @@
         </is>
       </c>
       <c r="D247" s="4">
+        <v>12</v>
+      </c>
+      <c r="E247" s="4">
         <v>2</v>
       </c>
-      <c r="E247" s="6" t="inlineStr">
+      <c r="F247" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22399,9 +23143,12 @@
         </is>
       </c>
       <c r="D248" s="4">
+        <v>12</v>
+      </c>
+      <c r="E248" s="4">
         <v>3</v>
       </c>
-      <c r="E248" s="6" t="inlineStr">
+      <c r="F248" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22515,9 +23262,12 @@
         </is>
       </c>
       <c r="D249" s="4">
+        <v>12</v>
+      </c>
+      <c r="E249" s="4">
         <v>4</v>
       </c>
-      <c r="E249" s="6" t="inlineStr">
+      <c r="F249" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22631,9 +23381,12 @@
         </is>
       </c>
       <c r="D250" s="4">
+        <v>12</v>
+      </c>
+      <c r="E250" s="4">
         <v>5</v>
       </c>
-      <c r="E250" s="6" t="inlineStr">
+      <c r="F250" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22747,9 +23500,12 @@
         </is>
       </c>
       <c r="D251" s="4">
+        <v>21</v>
+      </c>
+      <c r="E251" s="4">
         <v>1</v>
       </c>
-      <c r="E251" s="6" t="inlineStr">
+      <c r="F251" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22863,9 +23619,12 @@
         </is>
       </c>
       <c r="D252" s="4">
+        <v>21</v>
+      </c>
+      <c r="E252" s="4">
         <v>2</v>
       </c>
-      <c r="E252" s="6" t="inlineStr">
+      <c r="F252" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22979,9 +23738,12 @@
         </is>
       </c>
       <c r="D253" s="4">
+        <v>21</v>
+      </c>
+      <c r="E253" s="4">
         <v>3</v>
       </c>
-      <c r="E253" s="6" t="inlineStr">
+      <c r="F253" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23095,9 +23857,12 @@
         </is>
       </c>
       <c r="D254" s="4">
+        <v>21</v>
+      </c>
+      <c r="E254" s="4">
         <v>4</v>
       </c>
-      <c r="E254" s="6" t="inlineStr">
+      <c r="F254" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23211,9 +23976,12 @@
         </is>
       </c>
       <c r="D255" s="4">
+        <v>21</v>
+      </c>
+      <c r="E255" s="4">
         <v>5</v>
       </c>
-      <c r="E255" s="6" t="inlineStr">
+      <c r="F255" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23327,9 +24095,12 @@
         </is>
       </c>
       <c r="D256" s="4">
+        <v>8</v>
+      </c>
+      <c r="E256" s="4">
         <v>1</v>
       </c>
-      <c r="E256" s="6" t="inlineStr">
+      <c r="F256" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23450,9 +24221,12 @@
         </is>
       </c>
       <c r="D257" s="4">
+        <v>8</v>
+      </c>
+      <c r="E257" s="4">
         <v>2</v>
       </c>
-      <c r="E257" s="6" t="inlineStr">
+      <c r="F257" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23573,9 +24347,12 @@
         </is>
       </c>
       <c r="D258" s="4">
+        <v>8</v>
+      </c>
+      <c r="E258" s="4">
         <v>3</v>
       </c>
-      <c r="E258" s="6" t="inlineStr">
+      <c r="F258" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23696,9 +24473,12 @@
         </is>
       </c>
       <c r="D259" s="4">
+        <v>8</v>
+      </c>
+      <c r="E259" s="4">
         <v>4</v>
       </c>
-      <c r="E259" s="6" t="inlineStr">
+      <c r="F259" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23819,9 +24599,12 @@
         </is>
       </c>
       <c r="D260" s="4">
+        <v>7</v>
+      </c>
+      <c r="E260" s="4">
         <v>1</v>
       </c>
-      <c r="E260" s="6" t="inlineStr">
+      <c r="F260" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23942,9 +24725,12 @@
         </is>
       </c>
       <c r="D261" s="4">
+        <v>7</v>
+      </c>
+      <c r="E261" s="4">
         <v>2</v>
       </c>
-      <c r="E261" s="6" t="inlineStr">
+      <c r="F261" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24065,9 +24851,12 @@
         </is>
       </c>
       <c r="D262" s="4">
+        <v>7</v>
+      </c>
+      <c r="E262" s="4">
         <v>3</v>
       </c>
-      <c r="E262" s="6" t="inlineStr">
+      <c r="F262" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24188,9 +24977,12 @@
         </is>
       </c>
       <c r="D263" s="4">
+        <v>3</v>
+      </c>
+      <c r="E263" s="4">
         <v>1</v>
       </c>
-      <c r="E263" s="6" t="inlineStr">
+      <c r="F263" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24311,9 +25103,12 @@
         </is>
       </c>
       <c r="D264" s="4">
+        <v>3</v>
+      </c>
+      <c r="E264" s="4">
         <v>2</v>
       </c>
-      <c r="E264" s="6" t="inlineStr">
+      <c r="F264" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24436,7 +25231,10 @@
       <c r="D265" s="4">
         <v>1</v>
       </c>
-      <c r="E265" s="6" t="inlineStr">
+      <c r="E265" s="4">
+        <v>1</v>
+      </c>
+      <c r="F265" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24499,7 +25297,10 @@
       <c r="D266" s="4">
         <v>1</v>
       </c>
-      <c r="E266" s="6" t="inlineStr">
+      <c r="E266" s="4">
+        <v>1</v>
+      </c>
+      <c r="F266" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -24527,7 +25328,10 @@
       <c r="D267" s="4">
         <v>1</v>
       </c>
-      <c r="E267" s="6" t="inlineStr">
+      <c r="E267" s="4">
+        <v>1</v>
+      </c>
+      <c r="F267" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24613,7 +25417,10 @@
       <c r="D268" s="4">
         <v>1</v>
       </c>
-      <c r="E268" s="6" t="inlineStr">
+      <c r="E268" s="4">
+        <v>1</v>
+      </c>
+      <c r="F268" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24699,7 +25506,10 @@
       <c r="D269" s="4">
         <v>1</v>
       </c>
-      <c r="E269" s="6" t="inlineStr">
+      <c r="E269" s="4">
+        <v>1</v>
+      </c>
+      <c r="F269" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24783,9 +25593,12 @@
         </is>
       </c>
       <c r="D270" s="4">
+        <v>5</v>
+      </c>
+      <c r="E270" s="4">
         <v>1</v>
       </c>
-      <c r="E270" s="6" t="inlineStr">
+      <c r="F270" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24876,9 +25689,12 @@
         </is>
       </c>
       <c r="D271" s="4">
+        <v>5</v>
+      </c>
+      <c r="E271" s="4">
         <v>2</v>
       </c>
-      <c r="E271" s="6" t="inlineStr">
+      <c r="F271" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24969,9 +25785,12 @@
         </is>
       </c>
       <c r="D272" s="4">
+        <v>5</v>
+      </c>
+      <c r="E272" s="4">
         <v>3</v>
       </c>
-      <c r="E272" s="6" t="inlineStr">
+      <c r="F272" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25062,9 +25881,12 @@
         </is>
       </c>
       <c r="D273" s="4">
+        <v>5</v>
+      </c>
+      <c r="E273" s="4">
         <v>4</v>
       </c>
-      <c r="E273" s="6" t="inlineStr">
+      <c r="F273" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25157,7 +25979,10 @@
       <c r="D274" s="4">
         <v>1</v>
       </c>
-      <c r="E274" s="6" t="inlineStr">
+      <c r="E274" s="4">
+        <v>1</v>
+      </c>
+      <c r="F274" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25248,9 +26073,12 @@
         </is>
       </c>
       <c r="D275" s="4">
+        <v>5</v>
+      </c>
+      <c r="E275" s="4">
         <v>1</v>
       </c>
-      <c r="E275" s="6" t="inlineStr">
+      <c r="F275" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25349,9 +26177,12 @@
         </is>
       </c>
       <c r="D276" s="4">
+        <v>5</v>
+      </c>
+      <c r="E276" s="4">
         <v>2</v>
       </c>
-      <c r="E276" s="6" t="inlineStr">
+      <c r="F276" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25450,9 +26281,12 @@
         </is>
       </c>
       <c r="D277" s="4">
+        <v>5</v>
+      </c>
+      <c r="E277" s="4">
         <v>3</v>
       </c>
-      <c r="E277" s="6" t="inlineStr">
+      <c r="F277" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25551,9 +26385,12 @@
         </is>
       </c>
       <c r="D278" s="4">
+        <v>5</v>
+      </c>
+      <c r="E278" s="4">
         <v>4</v>
       </c>
-      <c r="E278" s="6" t="inlineStr">
+      <c r="F278" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25654,7 +26491,10 @@
       <c r="D279" s="4">
         <v>5</v>
       </c>
-      <c r="E279" s="6" t="inlineStr">
+      <c r="E279" s="4">
+        <v>5</v>
+      </c>
+      <c r="F279" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25753,9 +26593,12 @@
         </is>
       </c>
       <c r="D280" s="4">
+        <v>10</v>
+      </c>
+      <c r="E280" s="4">
         <v>1</v>
       </c>
-      <c r="E280" s="6" t="inlineStr">
+      <c r="F280" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25854,9 +26697,12 @@
         </is>
       </c>
       <c r="D281" s="4">
+        <v>10</v>
+      </c>
+      <c r="E281" s="4">
         <v>2</v>
       </c>
-      <c r="E281" s="6" t="inlineStr">
+      <c r="F281" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25955,9 +26801,12 @@
         </is>
       </c>
       <c r="D282" s="4">
+        <v>10</v>
+      </c>
+      <c r="E282" s="4">
         <v>3</v>
       </c>
-      <c r="E282" s="6" t="inlineStr">
+      <c r="F282" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26056,9 +26905,12 @@
         </is>
       </c>
       <c r="D283" s="4">
+        <v>10</v>
+      </c>
+      <c r="E283" s="4">
         <v>4</v>
       </c>
-      <c r="E283" s="6" t="inlineStr">
+      <c r="F283" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26157,9 +27009,12 @@
         </is>
       </c>
       <c r="D284" s="4">
+        <v>10</v>
+      </c>
+      <c r="E284" s="4">
         <v>5</v>
       </c>
-      <c r="E284" s="6" t="inlineStr">
+      <c r="F284" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26258,9 +27113,12 @@
         </is>
       </c>
       <c r="D285" s="4">
+        <v>12</v>
+      </c>
+      <c r="E285" s="4">
         <v>1</v>
       </c>
-      <c r="E285" s="6" t="inlineStr">
+      <c r="F285" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26359,9 +27217,12 @@
         </is>
       </c>
       <c r="D286" s="4">
+        <v>12</v>
+      </c>
+      <c r="E286" s="4">
         <v>2</v>
       </c>
-      <c r="E286" s="6" t="inlineStr">
+      <c r="F286" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26460,9 +27321,12 @@
         </is>
       </c>
       <c r="D287" s="4">
+        <v>12</v>
+      </c>
+      <c r="E287" s="4">
         <v>3</v>
       </c>
-      <c r="E287" s="6" t="inlineStr">
+      <c r="F287" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26561,9 +27425,12 @@
         </is>
       </c>
       <c r="D288" s="4">
+        <v>12</v>
+      </c>
+      <c r="E288" s="4">
         <v>4</v>
       </c>
-      <c r="E288" s="6" t="inlineStr">
+      <c r="F288" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26662,9 +27529,12 @@
         </is>
       </c>
       <c r="D289" s="4">
+        <v>12</v>
+      </c>
+      <c r="E289" s="4">
         <v>5</v>
       </c>
-      <c r="E289" s="6" t="inlineStr">
+      <c r="F289" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26763,9 +27633,12 @@
         </is>
       </c>
       <c r="D290" s="4">
+        <v>8</v>
+      </c>
+      <c r="E290" s="4">
         <v>1</v>
       </c>
-      <c r="E290" s="6" t="inlineStr">
+      <c r="F290" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26871,9 +27744,12 @@
         </is>
       </c>
       <c r="D291" s="4">
+        <v>8</v>
+      </c>
+      <c r="E291" s="4">
         <v>2</v>
       </c>
-      <c r="E291" s="6" t="inlineStr">
+      <c r="F291" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26979,9 +27855,12 @@
         </is>
       </c>
       <c r="D292" s="4">
+        <v>8</v>
+      </c>
+      <c r="E292" s="4">
         <v>3</v>
       </c>
-      <c r="E292" s="6" t="inlineStr">
+      <c r="F292" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27087,9 +27966,12 @@
         </is>
       </c>
       <c r="D293" s="4">
+        <v>8</v>
+      </c>
+      <c r="E293" s="4">
         <v>4</v>
       </c>
-      <c r="E293" s="6" t="inlineStr">
+      <c r="F293" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27195,9 +28077,12 @@
         </is>
       </c>
       <c r="D294" s="4">
+        <v>8</v>
+      </c>
+      <c r="E294" s="4">
         <v>5</v>
       </c>
-      <c r="E294" s="6" t="inlineStr">
+      <c r="F294" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27303,9 +28188,12 @@
         </is>
       </c>
       <c r="D295" s="4">
+        <v>10</v>
+      </c>
+      <c r="E295" s="4">
         <v>1</v>
       </c>
-      <c r="E295" s="6" t="inlineStr">
+      <c r="F295" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27411,9 +28299,12 @@
         </is>
       </c>
       <c r="D296" s="4">
+        <v>10</v>
+      </c>
+      <c r="E296" s="4">
         <v>2</v>
       </c>
-      <c r="E296" s="6" t="inlineStr">
+      <c r="F296" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27519,9 +28410,12 @@
         </is>
       </c>
       <c r="D297" s="4">
+        <v>10</v>
+      </c>
+      <c r="E297" s="4">
         <v>3</v>
       </c>
-      <c r="E297" s="6" t="inlineStr">
+      <c r="F297" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27627,9 +28521,12 @@
         </is>
       </c>
       <c r="D298" s="4">
+        <v>10</v>
+      </c>
+      <c r="E298" s="4">
         <v>4</v>
       </c>
-      <c r="E298" s="6" t="inlineStr">
+      <c r="F298" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27735,9 +28632,12 @@
         </is>
       </c>
       <c r="D299" s="4">
+        <v>10</v>
+      </c>
+      <c r="E299" s="4">
         <v>5</v>
       </c>
-      <c r="E299" s="6" t="inlineStr">
+      <c r="F299" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27843,9 +28743,12 @@
         </is>
       </c>
       <c r="D300" s="4">
+        <v>15</v>
+      </c>
+      <c r="E300" s="4">
         <v>1</v>
       </c>
-      <c r="E300" s="6" t="inlineStr">
+      <c r="F300" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27951,9 +28854,12 @@
         </is>
       </c>
       <c r="D301" s="4">
+        <v>15</v>
+      </c>
+      <c r="E301" s="4">
         <v>2</v>
       </c>
-      <c r="E301" s="6" t="inlineStr">
+      <c r="F301" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28059,9 +28965,12 @@
         </is>
       </c>
       <c r="D302" s="4">
+        <v>15</v>
+      </c>
+      <c r="E302" s="4">
         <v>3</v>
       </c>
-      <c r="E302" s="6" t="inlineStr">
+      <c r="F302" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28167,9 +29076,12 @@
         </is>
       </c>
       <c r="D303" s="4">
+        <v>15</v>
+      </c>
+      <c r="E303" s="4">
         <v>4</v>
       </c>
-      <c r="E303" s="6" t="inlineStr">
+      <c r="F303" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28275,9 +29187,12 @@
         </is>
       </c>
       <c r="D304" s="4">
+        <v>15</v>
+      </c>
+      <c r="E304" s="4">
         <v>5</v>
       </c>
-      <c r="E304" s="6" t="inlineStr">
+      <c r="F304" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28383,9 +29298,12 @@
         </is>
       </c>
       <c r="D305" s="4">
+        <v>10</v>
+      </c>
+      <c r="E305" s="4">
         <v>1</v>
       </c>
-      <c r="E305" s="6" t="inlineStr">
+      <c r="F305" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28499,9 +29417,12 @@
         </is>
       </c>
       <c r="D306" s="4">
+        <v>10</v>
+      </c>
+      <c r="E306" s="4">
         <v>2</v>
       </c>
-      <c r="E306" s="6" t="inlineStr">
+      <c r="F306" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28615,9 +29536,12 @@
         </is>
       </c>
       <c r="D307" s="4">
+        <v>10</v>
+      </c>
+      <c r="E307" s="4">
         <v>3</v>
       </c>
-      <c r="E307" s="6" t="inlineStr">
+      <c r="F307" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28731,9 +29655,12 @@
         </is>
       </c>
       <c r="D308" s="4">
+        <v>10</v>
+      </c>
+      <c r="E308" s="4">
         <v>4</v>
       </c>
-      <c r="E308" s="6" t="inlineStr">
+      <c r="F308" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28847,9 +29774,12 @@
         </is>
       </c>
       <c r="D309" s="4">
+        <v>10</v>
+      </c>
+      <c r="E309" s="4">
         <v>5</v>
       </c>
-      <c r="E309" s="6" t="inlineStr">
+      <c r="F309" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28963,9 +29893,12 @@
         </is>
       </c>
       <c r="D310" s="4">
+        <v>9</v>
+      </c>
+      <c r="E310" s="4">
         <v>1</v>
       </c>
-      <c r="E310" s="6" t="inlineStr">
+      <c r="F310" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29079,9 +30012,12 @@
         </is>
       </c>
       <c r="D311" s="4">
+        <v>9</v>
+      </c>
+      <c r="E311" s="4">
         <v>2</v>
       </c>
-      <c r="E311" s="6" t="inlineStr">
+      <c r="F311" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29195,9 +30131,12 @@
         </is>
       </c>
       <c r="D312" s="4">
+        <v>9</v>
+      </c>
+      <c r="E312" s="4">
         <v>3</v>
       </c>
-      <c r="E312" s="6" t="inlineStr">
+      <c r="F312" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29311,9 +30250,12 @@
         </is>
       </c>
       <c r="D313" s="4">
+        <v>9</v>
+      </c>
+      <c r="E313" s="4">
         <v>4</v>
       </c>
-      <c r="E313" s="6" t="inlineStr">
+      <c r="F313" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29427,9 +30369,12 @@
         </is>
       </c>
       <c r="D314" s="4">
+        <v>9</v>
+      </c>
+      <c r="E314" s="4">
         <v>5</v>
       </c>
-      <c r="E314" s="6" t="inlineStr">
+      <c r="F314" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29543,9 +30488,12 @@
         </is>
       </c>
       <c r="D315" s="4">
+        <v>15</v>
+      </c>
+      <c r="E315" s="4">
         <v>1</v>
       </c>
-      <c r="E315" s="6" t="inlineStr">
+      <c r="F315" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29659,9 +30607,12 @@
         </is>
       </c>
       <c r="D316" s="4">
+        <v>15</v>
+      </c>
+      <c r="E316" s="4">
         <v>2</v>
       </c>
-      <c r="E316" s="6" t="inlineStr">
+      <c r="F316" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29775,9 +30726,12 @@
         </is>
       </c>
       <c r="D317" s="4">
+        <v>15</v>
+      </c>
+      <c r="E317" s="4">
         <v>3</v>
       </c>
-      <c r="E317" s="6" t="inlineStr">
+      <c r="F317" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29891,9 +30845,12 @@
         </is>
       </c>
       <c r="D318" s="4">
+        <v>15</v>
+      </c>
+      <c r="E318" s="4">
         <v>4</v>
       </c>
-      <c r="E318" s="6" t="inlineStr">
+      <c r="F318" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30007,9 +30964,12 @@
         </is>
       </c>
       <c r="D319" s="4">
+        <v>15</v>
+      </c>
+      <c r="E319" s="4">
         <v>5</v>
       </c>
-      <c r="E319" s="6" t="inlineStr">
+      <c r="F319" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30123,9 +31083,12 @@
         </is>
       </c>
       <c r="D320" s="4">
+        <v>3</v>
+      </c>
+      <c r="E320" s="4">
         <v>1</v>
       </c>
-      <c r="E320" s="6" t="inlineStr">
+      <c r="F320" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30246,9 +31209,12 @@
         </is>
       </c>
       <c r="D321" s="4">
+        <v>4</v>
+      </c>
+      <c r="E321" s="4">
         <v>1</v>
       </c>
-      <c r="E321" s="6" t="inlineStr">
+      <c r="F321" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30369,9 +31335,12 @@
         </is>
       </c>
       <c r="D322" s="4">
+        <v>3</v>
+      </c>
+      <c r="E322" s="4">
         <v>1</v>
       </c>
-      <c r="E322" s="6" t="inlineStr">
+      <c r="F322" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30494,7 +31463,10 @@
       <c r="D323" s="4">
         <v>1</v>
       </c>
-      <c r="E323" s="6" t="inlineStr">
+      <c r="E323" s="4">
+        <v>1</v>
+      </c>
+      <c r="F323" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30550,7 +31522,10 @@
       <c r="D324" s="4">
         <v>1</v>
       </c>
-      <c r="E324" s="6" t="inlineStr">
+      <c r="E324" s="4">
+        <v>1</v>
+      </c>
+      <c r="F324" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30604,9 +31579,12 @@
         </is>
       </c>
       <c r="D325" s="4">
+        <v>2</v>
+      </c>
+      <c r="E325" s="4">
         <v>1</v>
       </c>
-      <c r="E325" s="6" t="inlineStr">
+      <c r="F325" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30662,7 +31640,10 @@
       <c r="D326" s="4">
         <v>2</v>
       </c>
-      <c r="E326" s="6" t="inlineStr">
+      <c r="E326" s="4">
+        <v>2</v>
+      </c>
+      <c r="F326" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30716,9 +31697,12 @@
         </is>
       </c>
       <c r="D327" s="4">
+        <v>3</v>
+      </c>
+      <c r="E327" s="4">
         <v>1</v>
       </c>
-      <c r="E327" s="6" t="inlineStr">
+      <c r="F327" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30772,9 +31756,12 @@
         </is>
       </c>
       <c r="D328" s="4">
+        <v>3</v>
+      </c>
+      <c r="E328" s="4">
         <v>2</v>
       </c>
-      <c r="E328" s="6" t="inlineStr">
+      <c r="F328" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30830,7 +31817,10 @@
       <c r="D329" s="4">
         <v>3</v>
       </c>
-      <c r="E329" s="6" t="inlineStr">
+      <c r="E329" s="4">
+        <v>3</v>
+      </c>
+      <c r="F329" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30886,7 +31876,10 @@
       <c r="D330" s="4">
         <v>1</v>
       </c>
-      <c r="E330" s="6" t="inlineStr">
+      <c r="E330" s="4">
+        <v>1</v>
+      </c>
+      <c r="F330" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30942,7 +31935,10 @@
       <c r="D331" s="4">
         <v>1</v>
       </c>
-      <c r="E331" s="6" t="inlineStr">
+      <c r="E331" s="4">
+        <v>1</v>
+      </c>
+      <c r="F331" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30998,7 +31994,10 @@
       <c r="D332" s="4">
         <v>1</v>
       </c>
-      <c r="E332" s="6" t="inlineStr">
+      <c r="E332" s="4">
+        <v>1</v>
+      </c>
+      <c r="F332" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31052,9 +32051,12 @@
         </is>
       </c>
       <c r="D333" s="4">
+        <v>3</v>
+      </c>
+      <c r="E333" s="4">
         <v>1</v>
       </c>
-      <c r="E333" s="6" t="inlineStr">
+      <c r="F333" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31108,9 +32110,12 @@
         </is>
       </c>
       <c r="D334" s="4">
+        <v>3</v>
+      </c>
+      <c r="E334" s="4">
         <v>2</v>
       </c>
-      <c r="E334" s="6" t="inlineStr">
+      <c r="F334" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31166,7 +32171,10 @@
       <c r="D335" s="4">
         <v>3</v>
       </c>
-      <c r="E335" s="6" t="inlineStr">
+      <c r="E335" s="4">
+        <v>3</v>
+      </c>
+      <c r="F335" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31222,7 +32230,10 @@
       <c r="D336" s="4">
         <v>1</v>
       </c>
-      <c r="E336" s="6" t="inlineStr">
+      <c r="E336" s="4">
+        <v>1</v>
+      </c>
+      <c r="F336" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31278,7 +32289,10 @@
       <c r="D337" s="4">
         <v>1</v>
       </c>
-      <c r="E337" s="6" t="inlineStr">
+      <c r="E337" s="4">
+        <v>1</v>
+      </c>
+      <c r="F337" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31332,9 +32346,12 @@
         </is>
       </c>
       <c r="D338" s="4">
+        <v>2</v>
+      </c>
+      <c r="E338" s="4">
         <v>1</v>
       </c>
-      <c r="E338" s="6" t="inlineStr">
+      <c r="F338" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31390,7 +32407,10 @@
       <c r="D339" s="4">
         <v>2</v>
       </c>
-      <c r="E339" s="6" t="inlineStr">
+      <c r="E339" s="4">
+        <v>2</v>
+      </c>
+      <c r="F339" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31444,9 +32464,12 @@
         </is>
       </c>
       <c r="D340" s="4">
+        <v>2</v>
+      </c>
+      <c r="E340" s="4">
         <v>1</v>
       </c>
-      <c r="E340" s="6" t="inlineStr">
+      <c r="F340" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31518,7 +32541,10 @@
       <c r="D341" s="4">
         <v>2</v>
       </c>
-      <c r="E341" s="6" t="inlineStr">
+      <c r="E341" s="4">
+        <v>2</v>
+      </c>
+      <c r="F341" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31588,9 +32614,12 @@
         </is>
       </c>
       <c r="D342" s="4">
+        <v>2</v>
+      </c>
+      <c r="E342" s="4">
         <v>1</v>
       </c>
-      <c r="E342" s="6" t="inlineStr">
+      <c r="F342" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31653,7 +32682,10 @@
       <c r="D343" s="4">
         <v>2</v>
       </c>
-      <c r="E343" s="6" t="inlineStr">
+      <c r="E343" s="4">
+        <v>2</v>
+      </c>
+      <c r="F343" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31714,9 +32746,12 @@
         </is>
       </c>
       <c r="D344" s="4">
+        <v>8</v>
+      </c>
+      <c r="E344" s="4">
         <v>1</v>
       </c>
-      <c r="E344" s="6" t="inlineStr">
+      <c r="F344" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31777,9 +32812,12 @@
         </is>
       </c>
       <c r="D345" s="4">
+        <v>8</v>
+      </c>
+      <c r="E345" s="4">
         <v>2</v>
       </c>
-      <c r="E345" s="6" t="inlineStr">
+      <c r="F345" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31840,9 +32878,12 @@
         </is>
       </c>
       <c r="D346" s="4">
+        <v>8</v>
+      </c>
+      <c r="E346" s="4">
         <v>3</v>
       </c>
-      <c r="E346" s="6" t="inlineStr">
+      <c r="F346" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31903,9 +32944,12 @@
         </is>
       </c>
       <c r="D347" s="4">
+        <v>8</v>
+      </c>
+      <c r="E347" s="4">
         <v>4</v>
       </c>
-      <c r="E347" s="6" t="inlineStr">
+      <c r="F347" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31966,9 +33010,12 @@
         </is>
       </c>
       <c r="D348" s="4">
+        <v>8</v>
+      </c>
+      <c r="E348" s="4">
         <v>5</v>
       </c>
-      <c r="E348" s="6" t="inlineStr">
+      <c r="F348" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32029,9 +33076,12 @@
         </is>
       </c>
       <c r="D349" s="4">
+        <v>8</v>
+      </c>
+      <c r="E349" s="4">
         <v>6</v>
       </c>
-      <c r="E349" s="6" t="inlineStr">
+      <c r="F349" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32092,9 +33142,12 @@
         </is>
       </c>
       <c r="D350" s="4">
+        <v>8</v>
+      </c>
+      <c r="E350" s="4">
         <v>7</v>
       </c>
-      <c r="E350" s="6" t="inlineStr">
+      <c r="F350" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32155,9 +33208,12 @@
         </is>
       </c>
       <c r="D351" s="4">
+        <v>2</v>
+      </c>
+      <c r="E351" s="4">
         <v>1</v>
       </c>
-      <c r="E351" s="6" t="inlineStr">
+      <c r="F351" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32228,7 +33284,10 @@
       <c r="D352" s="4">
         <v>2</v>
       </c>
-      <c r="E352" s="6" t="inlineStr">
+      <c r="E352" s="4">
+        <v>2</v>
+      </c>
+      <c r="F352" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32297,9 +33356,12 @@
         </is>
       </c>
       <c r="D353" s="4">
+        <v>2</v>
+      </c>
+      <c r="E353" s="4">
         <v>1</v>
       </c>
-      <c r="E353" s="6" t="inlineStr">
+      <c r="F353" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32400,7 +33462,10 @@
       <c r="D354" s="4">
         <v>2</v>
       </c>
-      <c r="E354" s="6" t="inlineStr">
+      <c r="E354" s="4">
+        <v>2</v>
+      </c>
+      <c r="F354" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32491,9 +33556,12 @@
         </is>
       </c>
       <c r="D355" s="4">
+        <v>4</v>
+      </c>
+      <c r="E355" s="4">
         <v>1</v>
       </c>
-      <c r="E355" s="6" t="inlineStr">
+      <c r="F355" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32554,9 +33622,12 @@
         </is>
       </c>
       <c r="D356" s="4">
+        <v>4</v>
+      </c>
+      <c r="E356" s="4">
         <v>2</v>
       </c>
-      <c r="E356" s="6" t="inlineStr">
+      <c r="F356" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32617,9 +33688,12 @@
         </is>
       </c>
       <c r="D357" s="4">
+        <v>4</v>
+      </c>
+      <c r="E357" s="4">
         <v>3</v>
       </c>
-      <c r="E357" s="6" t="inlineStr">
+      <c r="F357" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32682,7 +33756,10 @@
       <c r="D358" s="4">
         <v>4</v>
       </c>
-      <c r="E358" s="6" t="inlineStr">
+      <c r="E358" s="4">
+        <v>4</v>
+      </c>
+      <c r="F358" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32743,9 +33820,12 @@
         </is>
       </c>
       <c r="D359" s="4">
+        <v>4</v>
+      </c>
+      <c r="E359" s="4">
         <v>1</v>
       </c>
-      <c r="E359" s="6" t="inlineStr">
+      <c r="F359" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32814,9 +33894,12 @@
         </is>
       </c>
       <c r="D360" s="4">
+        <v>4</v>
+      </c>
+      <c r="E360" s="4">
         <v>2</v>
       </c>
-      <c r="E360" s="6" t="inlineStr">
+      <c r="F360" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32885,9 +33968,12 @@
         </is>
       </c>
       <c r="D361" s="4">
+        <v>4</v>
+      </c>
+      <c r="E361" s="4">
         <v>3</v>
       </c>
-      <c r="E361" s="6" t="inlineStr">
+      <c r="F361" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32958,7 +34044,10 @@
       <c r="D362" s="4">
         <v>4</v>
       </c>
-      <c r="E362" s="6" t="inlineStr">
+      <c r="E362" s="4">
+        <v>4</v>
+      </c>
+      <c r="F362" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33029,7 +34118,10 @@
       <c r="D363" s="4">
         <v>1</v>
       </c>
-      <c r="E363" s="6" t="inlineStr">
+      <c r="E363" s="4">
+        <v>1</v>
+      </c>
+      <c r="F363" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33105,9 +34197,12 @@
         </is>
       </c>
       <c r="D364" s="4">
+        <v>4</v>
+      </c>
+      <c r="E364" s="4">
         <v>1</v>
       </c>
-      <c r="E364" s="6" t="inlineStr">
+      <c r="F364" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33191,9 +34286,12 @@
         </is>
       </c>
       <c r="D365" s="4">
+        <v>4</v>
+      </c>
+      <c r="E365" s="4">
         <v>2</v>
       </c>
-      <c r="E365" s="6" t="inlineStr">
+      <c r="F365" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33284,9 +34382,12 @@
         </is>
       </c>
       <c r="D366" s="4">
+        <v>4</v>
+      </c>
+      <c r="E366" s="4">
         <v>3</v>
       </c>
-      <c r="E366" s="6" t="inlineStr">
+      <c r="F366" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33379,7 +34480,10 @@
       <c r="D367" s="4">
         <v>4</v>
       </c>
-      <c r="E367" s="6" t="inlineStr">
+      <c r="E367" s="4">
+        <v>4</v>
+      </c>
+      <c r="F367" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33472,7 +34576,10 @@
       <c r="D368" s="4">
         <v>1</v>
       </c>
-      <c r="E368" s="6" t="inlineStr">
+      <c r="E368" s="4">
+        <v>1</v>
+      </c>
+      <c r="F368" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33542,9 +34649,12 @@
         </is>
       </c>
       <c r="D369" s="4">
+        <v>5</v>
+      </c>
+      <c r="E369" s="4">
         <v>1</v>
       </c>
-      <c r="E369" s="6" t="inlineStr">
+      <c r="F369" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33605,9 +34715,12 @@
         </is>
       </c>
       <c r="D370" s="4">
+        <v>5</v>
+      </c>
+      <c r="E370" s="4">
         <v>2</v>
       </c>
-      <c r="E370" s="6" t="inlineStr">
+      <c r="F370" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33668,9 +34781,12 @@
         </is>
       </c>
       <c r="D371" s="4">
+        <v>5</v>
+      </c>
+      <c r="E371" s="4">
         <v>3</v>
       </c>
-      <c r="E371" s="6" t="inlineStr">
+      <c r="F371" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33731,9 +34847,12 @@
         </is>
       </c>
       <c r="D372" s="4">
+        <v>5</v>
+      </c>
+      <c r="E372" s="4">
         <v>4</v>
       </c>
-      <c r="E372" s="6" t="inlineStr">
+      <c r="F372" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33796,7 +34915,10 @@
       <c r="D373" s="4">
         <v>5</v>
       </c>
-      <c r="E373" s="6" t="inlineStr">
+      <c r="E373" s="4">
+        <v>5</v>
+      </c>
+      <c r="F373" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33859,7 +34981,10 @@
       <c r="D374" s="4">
         <v>1</v>
       </c>
-      <c r="E374" s="6" t="inlineStr">
+      <c r="E374" s="4">
+        <v>1</v>
+      </c>
+      <c r="F374" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33929,9 +35054,12 @@
         </is>
       </c>
       <c r="D375" s="4">
+        <v>3</v>
+      </c>
+      <c r="E375" s="4">
         <v>1</v>
       </c>
-      <c r="E375" s="6" t="inlineStr">
+      <c r="F375" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33992,9 +35120,12 @@
         </is>
       </c>
       <c r="D376" s="4">
+        <v>3</v>
+      </c>
+      <c r="E376" s="4">
         <v>2</v>
       </c>
-      <c r="E376" s="6" t="inlineStr">
+      <c r="F376" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34057,7 +35188,10 @@
       <c r="D377" s="4">
         <v>3</v>
       </c>
-      <c r="E377" s="6" t="inlineStr">
+      <c r="E377" s="4">
+        <v>3</v>
+      </c>
+      <c r="F377" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34120,7 +35254,10 @@
       <c r="D378" s="4">
         <v>1</v>
       </c>
-      <c r="E378" s="6" t="inlineStr">
+      <c r="E378" s="4">
+        <v>1</v>
+      </c>
+      <c r="F378" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34181,9 +35318,12 @@
         </is>
       </c>
       <c r="D379" s="4">
+        <v>2</v>
+      </c>
+      <c r="E379" s="4">
         <v>1</v>
       </c>
-      <c r="E379" s="6" t="inlineStr">
+      <c r="F379" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34255,7 +35395,10 @@
       <c r="D380" s="4">
         <v>2</v>
       </c>
-      <c r="E380" s="6" t="inlineStr">
+      <c r="E380" s="4">
+        <v>2</v>
+      </c>
+      <c r="F380" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34325,9 +35468,12 @@
         </is>
       </c>
       <c r="D381" s="4">
+        <v>3</v>
+      </c>
+      <c r="E381" s="4">
         <v>1</v>
       </c>
-      <c r="E381" s="6" t="inlineStr">
+      <c r="F381" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34397,9 +35543,12 @@
         </is>
       </c>
       <c r="D382" s="4">
+        <v>3</v>
+      </c>
+      <c r="E382" s="4">
         <v>2</v>
       </c>
-      <c r="E382" s="6" t="inlineStr">
+      <c r="F382" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34471,7 +35620,10 @@
       <c r="D383" s="4">
         <v>3</v>
       </c>
-      <c r="E383" s="6" t="inlineStr">
+      <c r="E383" s="4">
+        <v>3</v>
+      </c>
+      <c r="F383" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34543,7 +35695,10 @@
       <c r="D384" s="4">
         <v>1</v>
       </c>
-      <c r="E384" s="6" t="inlineStr">
+      <c r="E384" s="4">
+        <v>1</v>
+      </c>
+      <c r="F384" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34612,9 +35767,12 @@
         </is>
       </c>
       <c r="D385" s="4">
+        <v>2</v>
+      </c>
+      <c r="E385" s="4">
         <v>1</v>
       </c>
-      <c r="E385" s="6" t="inlineStr">
+      <c r="F385" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34700,7 +35858,10 @@
       <c r="D386" s="4">
         <v>2</v>
       </c>
-      <c r="E386" s="6" t="inlineStr">
+      <c r="E386" s="4">
+        <v>2</v>
+      </c>
+      <c r="F386" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34784,9 +35945,12 @@
         </is>
       </c>
       <c r="D387" s="4">
+        <v>13</v>
+      </c>
+      <c r="E387" s="4">
         <v>1</v>
       </c>
-      <c r="E387" s="6" t="inlineStr">
+      <c r="F387" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34885,9 +36049,12 @@
         </is>
       </c>
       <c r="D388" s="4">
+        <v>13</v>
+      </c>
+      <c r="E388" s="4">
         <v>2</v>
       </c>
-      <c r="E388" s="6" t="inlineStr">
+      <c r="F388" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34978,9 +36145,12 @@
         </is>
       </c>
       <c r="D389" s="4">
+        <v>13</v>
+      </c>
+      <c r="E389" s="4">
         <v>3</v>
       </c>
-      <c r="E389" s="6" t="inlineStr">
+      <c r="F389" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35071,9 +36241,12 @@
         </is>
       </c>
       <c r="D390" s="4">
+        <v>13</v>
+      </c>
+      <c r="E390" s="4">
         <v>4</v>
       </c>
-      <c r="E390" s="6" t="inlineStr">
+      <c r="F390" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35164,9 +36337,12 @@
         </is>
       </c>
       <c r="D391" s="4">
+        <v>13</v>
+      </c>
+      <c r="E391" s="4">
         <v>5</v>
       </c>
-      <c r="E391" s="6" t="inlineStr">
+      <c r="F391" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35272,9 +36448,12 @@
         </is>
       </c>
       <c r="D392" s="4">
+        <v>13</v>
+      </c>
+      <c r="E392" s="4">
         <v>6</v>
       </c>
-      <c r="E392" s="6" t="inlineStr">
+      <c r="F392" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35395,9 +36574,12 @@
         </is>
       </c>
       <c r="D393" s="4">
+        <v>13</v>
+      </c>
+      <c r="E393" s="4">
         <v>7</v>
       </c>
-      <c r="E393" s="6" t="inlineStr">
+      <c r="F393" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35488,9 +36670,12 @@
         </is>
       </c>
       <c r="D394" s="4">
+        <v>13</v>
+      </c>
+      <c r="E394" s="4">
         <v>8</v>
       </c>
-      <c r="E394" s="6" t="inlineStr">
+      <c r="F394" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35581,9 +36766,12 @@
         </is>
       </c>
       <c r="D395" s="4">
+        <v>13</v>
+      </c>
+      <c r="E395" s="4">
         <v>9</v>
       </c>
-      <c r="E395" s="6" t="inlineStr">
+      <c r="F395" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35682,9 +36870,12 @@
         </is>
       </c>
       <c r="D396" s="4">
+        <v>13</v>
+      </c>
+      <c r="E396" s="4">
         <v>10</v>
       </c>
-      <c r="E396" s="6" t="inlineStr">
+      <c r="F396" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35783,9 +36974,12 @@
         </is>
       </c>
       <c r="D397" s="4">
+        <v>13</v>
+      </c>
+      <c r="E397" s="4">
         <v>11</v>
       </c>
-      <c r="E397" s="6" t="inlineStr">
+      <c r="F397" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35884,9 +37078,12 @@
         </is>
       </c>
       <c r="D398" s="4">
+        <v>13</v>
+      </c>
+      <c r="E398" s="4">
         <v>12</v>
       </c>
-      <c r="E398" s="6" t="inlineStr">
+      <c r="F398" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35987,7 +37184,10 @@
       <c r="D399" s="4">
         <v>13</v>
       </c>
-      <c r="E399" s="6" t="inlineStr">
+      <c r="E399" s="4">
+        <v>13</v>
+      </c>
+      <c r="F399" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36095,7 +37295,10 @@
       <c r="D400" s="4">
         <v>1</v>
       </c>
-      <c r="E400" s="6" t="inlineStr">
+      <c r="E400" s="4">
+        <v>1</v>
+      </c>
+      <c r="F400" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36158,7 +37361,10 @@
       <c r="D401" s="4">
         <v>1</v>
       </c>
-      <c r="E401" s="6" t="inlineStr">
+      <c r="E401" s="4">
+        <v>1</v>
+      </c>
+      <c r="F401" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36229,7 +37435,10 @@
       <c r="D402" s="4">
         <v>1</v>
       </c>
-      <c r="E402" s="6" t="inlineStr">
+      <c r="E402" s="4">
+        <v>1</v>
+      </c>
+      <c r="F402" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36292,7 +37501,10 @@
       <c r="D403" s="4">
         <v>1</v>
       </c>
-      <c r="E403" s="6" t="inlineStr">
+      <c r="E403" s="4">
+        <v>1</v>
+      </c>
+      <c r="F403" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36391,9 +37603,12 @@
         </is>
       </c>
       <c r="D404" s="4">
+        <v>6</v>
+      </c>
+      <c r="E404" s="4">
         <v>1</v>
       </c>
-      <c r="E404" s="6" t="inlineStr">
+      <c r="F404" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36454,9 +37669,12 @@
         </is>
       </c>
       <c r="D405" s="4">
+        <v>6</v>
+      </c>
+      <c r="E405" s="4">
         <v>2</v>
       </c>
-      <c r="E405" s="6" t="inlineStr">
+      <c r="F405" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36517,9 +37735,12 @@
         </is>
       </c>
       <c r="D406" s="4">
+        <v>6</v>
+      </c>
+      <c r="E406" s="4">
         <v>3</v>
       </c>
-      <c r="E406" s="6" t="inlineStr">
+      <c r="F406" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36580,9 +37801,12 @@
         </is>
       </c>
       <c r="D407" s="4">
+        <v>6</v>
+      </c>
+      <c r="E407" s="4">
         <v>4</v>
       </c>
-      <c r="E407" s="6" t="inlineStr">
+      <c r="F407" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36643,9 +37867,12 @@
         </is>
       </c>
       <c r="D408" s="4">
+        <v>6</v>
+      </c>
+      <c r="E408" s="4">
         <v>5</v>
       </c>
-      <c r="E408" s="6" t="inlineStr">
+      <c r="F408" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36708,7 +37935,10 @@
       <c r="D409" s="4">
         <v>6</v>
       </c>
-      <c r="E409" s="6" t="inlineStr">
+      <c r="E409" s="4">
+        <v>6</v>
+      </c>
+      <c r="F409" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36771,7 +38001,10 @@
       <c r="D410" s="4">
         <v>1</v>
       </c>
-      <c r="E410" s="6" t="inlineStr">
+      <c r="E410" s="4">
+        <v>1</v>
+      </c>
+      <c r="F410" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36840,9 +38073,12 @@
         </is>
       </c>
       <c r="D411" s="4">
+        <v>8</v>
+      </c>
+      <c r="E411" s="4">
         <v>1</v>
       </c>
-      <c r="E411" s="6" t="inlineStr">
+      <c r="F411" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36912,9 +38148,12 @@
         </is>
       </c>
       <c r="D412" s="4">
+        <v>8</v>
+      </c>
+      <c r="E412" s="4">
         <v>2</v>
       </c>
-      <c r="E412" s="6" t="inlineStr">
+      <c r="F412" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36984,9 +38223,12 @@
         </is>
       </c>
       <c r="D413" s="4">
+        <v>8</v>
+      </c>
+      <c r="E413" s="4">
         <v>3</v>
       </c>
-      <c r="E413" s="6" t="inlineStr">
+      <c r="F413" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37056,9 +38298,12 @@
         </is>
       </c>
       <c r="D414" s="4">
+        <v>8</v>
+      </c>
+      <c r="E414" s="4">
         <v>4</v>
       </c>
-      <c r="E414" s="6" t="inlineStr">
+      <c r="F414" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37128,9 +38373,12 @@
         </is>
       </c>
       <c r="D415" s="4">
+        <v>8</v>
+      </c>
+      <c r="E415" s="4">
         <v>5</v>
       </c>
-      <c r="E415" s="6" t="inlineStr">
+      <c r="F415" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37200,9 +38448,12 @@
         </is>
       </c>
       <c r="D416" s="4">
+        <v>8</v>
+      </c>
+      <c r="E416" s="4">
         <v>6</v>
       </c>
-      <c r="E416" s="6" t="inlineStr">
+      <c r="F416" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37272,9 +38523,12 @@
         </is>
       </c>
       <c r="D417" s="4">
+        <v>8</v>
+      </c>
+      <c r="E417" s="4">
         <v>7</v>
       </c>
-      <c r="E417" s="6" t="inlineStr">
+      <c r="F417" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37346,7 +38600,10 @@
       <c r="D418" s="4">
         <v>1</v>
       </c>
-      <c r="E418" s="6" t="inlineStr">
+      <c r="E418" s="4">
+        <v>1</v>
+      </c>
+      <c r="F418" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37418,7 +38675,10 @@
       <c r="D419" s="4">
         <v>1</v>
       </c>
-      <c r="E419" s="6" t="inlineStr">
+      <c r="E419" s="4">
+        <v>1</v>
+      </c>
+      <c r="F419" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37481,7 +38741,10 @@
       <c r="D420" s="4">
         <v>1</v>
       </c>
-      <c r="E420" s="6" t="inlineStr">
+      <c r="E420" s="4">
+        <v>1</v>
+      </c>
+      <c r="F420" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37553,7 +38816,10 @@
       <c r="D421" s="4">
         <v>1</v>
       </c>
-      <c r="E421" s="6" t="inlineStr">
+      <c r="E421" s="4">
+        <v>1</v>
+      </c>
+      <c r="F421" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37623,9 +38889,12 @@
         </is>
       </c>
       <c r="D422" s="4">
+        <v>3</v>
+      </c>
+      <c r="E422" s="4">
         <v>1</v>
       </c>
-      <c r="E422" s="6" t="inlineStr">
+      <c r="F422" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37695,9 +38964,12 @@
         </is>
       </c>
       <c r="D423" s="4">
+        <v>3</v>
+      </c>
+      <c r="E423" s="4">
         <v>2</v>
       </c>
-      <c r="E423" s="6" t="inlineStr">
+      <c r="F423" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37769,7 +39041,10 @@
       <c r="D424" s="4">
         <v>3</v>
       </c>
-      <c r="E424" s="6" t="inlineStr">
+      <c r="E424" s="4">
+        <v>3</v>
+      </c>
+      <c r="F424" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37841,7 +39116,10 @@
       <c r="D425" s="4">
         <v>1</v>
       </c>
-      <c r="E425" s="6" t="inlineStr">
+      <c r="E425" s="4">
+        <v>1</v>
+      </c>
+      <c r="F425" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37902,9 +39180,12 @@
         </is>
       </c>
       <c r="D426" s="4">
+        <v>5</v>
+      </c>
+      <c r="E426" s="4">
         <v>1</v>
       </c>
-      <c r="E426" s="6" t="inlineStr">
+      <c r="F426" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37974,9 +39255,12 @@
         </is>
       </c>
       <c r="D427" s="4">
+        <v>5</v>
+      </c>
+      <c r="E427" s="4">
         <v>2</v>
       </c>
-      <c r="E427" s="6" t="inlineStr">
+      <c r="F427" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38046,9 +39330,12 @@
         </is>
       </c>
       <c r="D428" s="4">
+        <v>5</v>
+      </c>
+      <c r="E428" s="4">
         <v>3</v>
       </c>
-      <c r="E428" s="6" t="inlineStr">
+      <c r="F428" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38118,9 +39405,12 @@
         </is>
       </c>
       <c r="D429" s="4">
+        <v>5</v>
+      </c>
+      <c r="E429" s="4">
         <v>4</v>
       </c>
-      <c r="E429" s="6" t="inlineStr">
+      <c r="F429" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38192,7 +39482,10 @@
       <c r="D430" s="4">
         <v>5</v>
       </c>
-      <c r="E430" s="6" t="inlineStr">
+      <c r="E430" s="4">
+        <v>5</v>
+      </c>
+      <c r="F430" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38264,7 +39557,10 @@
       <c r="D431" s="4">
         <v>1</v>
       </c>
-      <c r="E431" s="6" t="inlineStr">
+      <c r="E431" s="4">
+        <v>1</v>
+      </c>
+      <c r="F431" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38336,7 +39632,10 @@
       <c r="D432" s="4">
         <v>1</v>
       </c>
-      <c r="E432" s="6" t="inlineStr">
+      <c r="E432" s="4">
+        <v>1</v>
+      </c>
+      <c r="F432" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38408,7 +39707,10 @@
       <c r="D433" s="4">
         <v>1</v>
       </c>
-      <c r="E433" s="6" t="inlineStr">
+      <c r="E433" s="4">
+        <v>1</v>
+      </c>
+      <c r="F433" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38478,9 +39780,12 @@
         </is>
       </c>
       <c r="D434" s="4">
+        <v>7</v>
+      </c>
+      <c r="E434" s="4">
         <v>1</v>
       </c>
-      <c r="E434" s="6" t="inlineStr">
+      <c r="F434" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38550,9 +39855,12 @@
         </is>
       </c>
       <c r="D435" s="4">
+        <v>7</v>
+      </c>
+      <c r="E435" s="4">
         <v>2</v>
       </c>
-      <c r="E435" s="6" t="inlineStr">
+      <c r="F435" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38622,9 +39930,12 @@
         </is>
       </c>
       <c r="D436" s="4">
+        <v>7</v>
+      </c>
+      <c r="E436" s="4">
         <v>3</v>
       </c>
-      <c r="E436" s="6" t="inlineStr">
+      <c r="F436" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38694,9 +40005,12 @@
         </is>
       </c>
       <c r="D437" s="4">
+        <v>7</v>
+      </c>
+      <c r="E437" s="4">
         <v>4</v>
       </c>
-      <c r="E437" s="6" t="inlineStr">
+      <c r="F437" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38766,9 +40080,12 @@
         </is>
       </c>
       <c r="D438" s="4">
+        <v>7</v>
+      </c>
+      <c r="E438" s="4">
         <v>5</v>
       </c>
-      <c r="E438" s="6" t="inlineStr">
+      <c r="F438" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38838,9 +40155,12 @@
         </is>
       </c>
       <c r="D439" s="4">
+        <v>7</v>
+      </c>
+      <c r="E439" s="4">
         <v>6</v>
       </c>
-      <c r="E439" s="6" t="inlineStr">
+      <c r="F439" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38912,7 +40232,10 @@
       <c r="D440" s="4">
         <v>7</v>
       </c>
-      <c r="E440" s="6" t="inlineStr">
+      <c r="E440" s="4">
+        <v>7</v>
+      </c>
+      <c r="F440" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38984,7 +40307,10 @@
       <c r="D441" s="4">
         <v>1</v>
       </c>
-      <c r="E441" s="6" t="inlineStr">
+      <c r="E441" s="4">
+        <v>1</v>
+      </c>
+      <c r="F441" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39054,9 +40380,12 @@
         </is>
       </c>
       <c r="D442" s="4">
+        <v>5</v>
+      </c>
+      <c r="E442" s="4">
         <v>1</v>
       </c>
-      <c r="E442" s="6" t="inlineStr">
+      <c r="F442" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39126,9 +40455,12 @@
         </is>
       </c>
       <c r="D443" s="4">
+        <v>5</v>
+      </c>
+      <c r="E443" s="4">
         <v>2</v>
       </c>
-      <c r="E443" s="6" t="inlineStr">
+      <c r="F443" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39198,9 +40530,12 @@
         </is>
       </c>
       <c r="D444" s="4">
+        <v>5</v>
+      </c>
+      <c r="E444" s="4">
         <v>3</v>
       </c>
-      <c r="E444" s="6" t="inlineStr">
+      <c r="F444" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39270,9 +40605,12 @@
         </is>
       </c>
       <c r="D445" s="4">
+        <v>5</v>
+      </c>
+      <c r="E445" s="4">
         <v>4</v>
       </c>
-      <c r="E445" s="6" t="inlineStr">
+      <c r="F445" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39344,7 +40682,10 @@
       <c r="D446" s="4">
         <v>5</v>
       </c>
-      <c r="E446" s="6" t="inlineStr">
+      <c r="E446" s="4">
+        <v>5</v>
+      </c>
+      <c r="F446" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39416,7 +40757,10 @@
       <c r="D447" s="4">
         <v>1</v>
       </c>
-      <c r="E447" s="6" t="inlineStr">
+      <c r="E447" s="4">
+        <v>1</v>
+      </c>
+      <c r="F447" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39488,7 +40832,10 @@
       <c r="D448" s="4">
         <v>1</v>
       </c>
-      <c r="E448" s="6" t="inlineStr">
+      <c r="E448" s="4">
+        <v>1</v>
+      </c>
+      <c r="F448" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39558,9 +40905,12 @@
         </is>
       </c>
       <c r="D449" s="4">
+        <v>4</v>
+      </c>
+      <c r="E449" s="4">
         <v>1</v>
       </c>
-      <c r="E449" s="6" t="inlineStr">
+      <c r="F449" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39630,9 +40980,12 @@
         </is>
       </c>
       <c r="D450" s="4">
+        <v>4</v>
+      </c>
+      <c r="E450" s="4">
         <v>2</v>
       </c>
-      <c r="E450" s="6" t="inlineStr">
+      <c r="F450" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39702,9 +41055,12 @@
         </is>
       </c>
       <c r="D451" s="4">
+        <v>4</v>
+      </c>
+      <c r="E451" s="4">
         <v>3</v>
       </c>
-      <c r="E451" s="6" t="inlineStr">
+      <c r="F451" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39776,7 +41132,10 @@
       <c r="D452" s="4">
         <v>4</v>
       </c>
-      <c r="E452" s="6" t="inlineStr">
+      <c r="E452" s="4">
+        <v>4</v>
+      </c>
+      <c r="F452" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39830,271 +41189,359 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="264">
+  <mergeCells count="352">
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
     <mergeCell ref="A30:A31"/>
     <mergeCell ref="B30:B31"/>
     <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
     <mergeCell ref="A32:A34"/>
     <mergeCell ref="B32:B34"/>
     <mergeCell ref="C32:C34"/>
+    <mergeCell ref="D32:D34"/>
     <mergeCell ref="A41:A42"/>
     <mergeCell ref="B41:B42"/>
     <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
     <mergeCell ref="A43:A44"/>
     <mergeCell ref="B43:B44"/>
     <mergeCell ref="C43:C44"/>
+    <mergeCell ref="D43:D44"/>
     <mergeCell ref="A45:A46"/>
     <mergeCell ref="B45:B46"/>
     <mergeCell ref="C45:C46"/>
+    <mergeCell ref="D45:D46"/>
     <mergeCell ref="A47:A49"/>
     <mergeCell ref="B47:B49"/>
     <mergeCell ref="C47:C49"/>
+    <mergeCell ref="D47:D49"/>
     <mergeCell ref="A50:A54"/>
     <mergeCell ref="B50:B54"/>
     <mergeCell ref="C50:C54"/>
+    <mergeCell ref="D50:D54"/>
     <mergeCell ref="A55:A56"/>
     <mergeCell ref="B55:B56"/>
     <mergeCell ref="C55:C56"/>
+    <mergeCell ref="D55:D56"/>
     <mergeCell ref="A59:A60"/>
     <mergeCell ref="B59:B60"/>
     <mergeCell ref="C59:C60"/>
+    <mergeCell ref="D59:D60"/>
     <mergeCell ref="A61:A63"/>
     <mergeCell ref="B61:B63"/>
     <mergeCell ref="C61:C63"/>
+    <mergeCell ref="D61:D63"/>
     <mergeCell ref="A73:A75"/>
     <mergeCell ref="B73:B75"/>
     <mergeCell ref="C73:C75"/>
+    <mergeCell ref="D73:D75"/>
     <mergeCell ref="A76:A77"/>
     <mergeCell ref="B76:B77"/>
     <mergeCell ref="C76:C77"/>
+    <mergeCell ref="D76:D77"/>
     <mergeCell ref="A79:A83"/>
     <mergeCell ref="B79:B83"/>
     <mergeCell ref="C79:C83"/>
+    <mergeCell ref="D79:D83"/>
     <mergeCell ref="A86:A87"/>
     <mergeCell ref="B86:B87"/>
     <mergeCell ref="C86:C87"/>
+    <mergeCell ref="D86:D87"/>
     <mergeCell ref="A88:A89"/>
     <mergeCell ref="B88:B89"/>
     <mergeCell ref="C88:C89"/>
+    <mergeCell ref="D88:D89"/>
     <mergeCell ref="A94:A95"/>
     <mergeCell ref="B94:B95"/>
     <mergeCell ref="C94:C95"/>
+    <mergeCell ref="D94:D95"/>
     <mergeCell ref="A99:A100"/>
     <mergeCell ref="B99:B100"/>
     <mergeCell ref="C99:C100"/>
+    <mergeCell ref="D99:D100"/>
     <mergeCell ref="A101:A103"/>
     <mergeCell ref="B101:B103"/>
     <mergeCell ref="C101:C103"/>
+    <mergeCell ref="D101:D103"/>
     <mergeCell ref="A106:A107"/>
     <mergeCell ref="B106:B107"/>
     <mergeCell ref="C106:C107"/>
+    <mergeCell ref="D106:D107"/>
     <mergeCell ref="A114:A115"/>
     <mergeCell ref="B114:B115"/>
     <mergeCell ref="C114:C115"/>
+    <mergeCell ref="D114:D115"/>
     <mergeCell ref="A122:A123"/>
     <mergeCell ref="B122:B123"/>
     <mergeCell ref="C122:C123"/>
+    <mergeCell ref="D122:D123"/>
     <mergeCell ref="A132:A133"/>
     <mergeCell ref="B132:B133"/>
     <mergeCell ref="C132:C133"/>
+    <mergeCell ref="D132:D133"/>
     <mergeCell ref="A136:A137"/>
     <mergeCell ref="B136:B137"/>
     <mergeCell ref="C136:C137"/>
+    <mergeCell ref="D136:D137"/>
     <mergeCell ref="A138:A139"/>
     <mergeCell ref="B138:B139"/>
     <mergeCell ref="C138:C139"/>
+    <mergeCell ref="D138:D139"/>
     <mergeCell ref="A140:A141"/>
     <mergeCell ref="B140:B141"/>
     <mergeCell ref="C140:C141"/>
+    <mergeCell ref="D140:D141"/>
     <mergeCell ref="A142:A146"/>
     <mergeCell ref="B142:B146"/>
     <mergeCell ref="C142:C146"/>
+    <mergeCell ref="D142:D146"/>
     <mergeCell ref="A147:A151"/>
     <mergeCell ref="B147:B151"/>
     <mergeCell ref="C147:C151"/>
+    <mergeCell ref="D147:D151"/>
     <mergeCell ref="A152:A156"/>
     <mergeCell ref="B152:B156"/>
     <mergeCell ref="C152:C156"/>
+    <mergeCell ref="D152:D156"/>
     <mergeCell ref="A157:A161"/>
     <mergeCell ref="B157:B161"/>
     <mergeCell ref="C157:C161"/>
+    <mergeCell ref="D157:D161"/>
     <mergeCell ref="A162:A166"/>
     <mergeCell ref="B162:B166"/>
     <mergeCell ref="C162:C166"/>
+    <mergeCell ref="D162:D166"/>
     <mergeCell ref="A167:A171"/>
     <mergeCell ref="B167:B171"/>
     <mergeCell ref="C167:C171"/>
+    <mergeCell ref="D167:D171"/>
     <mergeCell ref="A172:A176"/>
     <mergeCell ref="B172:B176"/>
     <mergeCell ref="C172:C176"/>
+    <mergeCell ref="D172:D176"/>
     <mergeCell ref="A177:A181"/>
     <mergeCell ref="B177:B181"/>
     <mergeCell ref="C177:C181"/>
+    <mergeCell ref="D177:D181"/>
     <mergeCell ref="A182:A186"/>
     <mergeCell ref="B182:B186"/>
     <mergeCell ref="C182:C186"/>
+    <mergeCell ref="D182:D186"/>
     <mergeCell ref="A187:A191"/>
     <mergeCell ref="B187:B191"/>
     <mergeCell ref="C187:C191"/>
+    <mergeCell ref="D187:D191"/>
     <mergeCell ref="A192:A196"/>
     <mergeCell ref="B192:B196"/>
     <mergeCell ref="C192:C196"/>
+    <mergeCell ref="D192:D196"/>
     <mergeCell ref="A197:A198"/>
     <mergeCell ref="B197:B198"/>
     <mergeCell ref="C197:C198"/>
+    <mergeCell ref="D197:D198"/>
     <mergeCell ref="A199:A201"/>
     <mergeCell ref="B199:B201"/>
     <mergeCell ref="C199:C201"/>
+    <mergeCell ref="D199:D201"/>
     <mergeCell ref="A206:A207"/>
     <mergeCell ref="B206:B207"/>
     <mergeCell ref="C206:C207"/>
+    <mergeCell ref="D206:D207"/>
     <mergeCell ref="A211:A212"/>
     <mergeCell ref="B211:B212"/>
     <mergeCell ref="C211:C212"/>
+    <mergeCell ref="D211:D212"/>
     <mergeCell ref="A213:A217"/>
     <mergeCell ref="B213:B217"/>
     <mergeCell ref="C213:C217"/>
+    <mergeCell ref="D213:D217"/>
     <mergeCell ref="A218:A222"/>
     <mergeCell ref="B218:B222"/>
     <mergeCell ref="C218:C222"/>
+    <mergeCell ref="D218:D222"/>
     <mergeCell ref="A223:A227"/>
     <mergeCell ref="B223:B227"/>
     <mergeCell ref="C223:C227"/>
+    <mergeCell ref="D223:D227"/>
     <mergeCell ref="A228:A231"/>
     <mergeCell ref="B228:B231"/>
     <mergeCell ref="C228:C231"/>
+    <mergeCell ref="D228:D231"/>
     <mergeCell ref="A232:A235"/>
     <mergeCell ref="B232:B235"/>
     <mergeCell ref="C232:C235"/>
+    <mergeCell ref="D232:D235"/>
     <mergeCell ref="A236:A240"/>
     <mergeCell ref="B236:B240"/>
     <mergeCell ref="C236:C240"/>
+    <mergeCell ref="D236:D240"/>
     <mergeCell ref="A241:A245"/>
     <mergeCell ref="B241:B245"/>
     <mergeCell ref="C241:C245"/>
+    <mergeCell ref="D241:D245"/>
     <mergeCell ref="A246:A250"/>
     <mergeCell ref="B246:B250"/>
     <mergeCell ref="C246:C250"/>
+    <mergeCell ref="D246:D250"/>
     <mergeCell ref="A251:A255"/>
     <mergeCell ref="B251:B255"/>
     <mergeCell ref="C251:C255"/>
+    <mergeCell ref="D251:D255"/>
     <mergeCell ref="A256:A259"/>
     <mergeCell ref="B256:B259"/>
     <mergeCell ref="C256:C259"/>
+    <mergeCell ref="D256:D259"/>
     <mergeCell ref="A260:A262"/>
     <mergeCell ref="B260:B262"/>
     <mergeCell ref="C260:C262"/>
+    <mergeCell ref="D260:D262"/>
     <mergeCell ref="A263:A264"/>
     <mergeCell ref="B263:B264"/>
     <mergeCell ref="C263:C264"/>
+    <mergeCell ref="D263:D264"/>
     <mergeCell ref="A270:A273"/>
     <mergeCell ref="B270:B273"/>
     <mergeCell ref="C270:C273"/>
+    <mergeCell ref="D270:D273"/>
     <mergeCell ref="A275:A279"/>
     <mergeCell ref="B275:B279"/>
     <mergeCell ref="C275:C279"/>
+    <mergeCell ref="D275:D279"/>
     <mergeCell ref="A280:A284"/>
     <mergeCell ref="B280:B284"/>
     <mergeCell ref="C280:C284"/>
+    <mergeCell ref="D280:D284"/>
     <mergeCell ref="A285:A289"/>
     <mergeCell ref="B285:B289"/>
     <mergeCell ref="C285:C289"/>
+    <mergeCell ref="D285:D289"/>
     <mergeCell ref="A290:A294"/>
     <mergeCell ref="B290:B294"/>
     <mergeCell ref="C290:C294"/>
+    <mergeCell ref="D290:D294"/>
     <mergeCell ref="A295:A299"/>
     <mergeCell ref="B295:B299"/>
     <mergeCell ref="C295:C299"/>
+    <mergeCell ref="D295:D299"/>
     <mergeCell ref="A300:A304"/>
     <mergeCell ref="B300:B304"/>
     <mergeCell ref="C300:C304"/>
+    <mergeCell ref="D300:D304"/>
     <mergeCell ref="A305:A309"/>
     <mergeCell ref="B305:B309"/>
     <mergeCell ref="C305:C309"/>
+    <mergeCell ref="D305:D309"/>
     <mergeCell ref="A310:A314"/>
     <mergeCell ref="B310:B314"/>
     <mergeCell ref="C310:C314"/>
+    <mergeCell ref="D310:D314"/>
     <mergeCell ref="A315:A319"/>
     <mergeCell ref="B315:B319"/>
     <mergeCell ref="C315:C319"/>
+    <mergeCell ref="D315:D319"/>
     <mergeCell ref="A325:A326"/>
     <mergeCell ref="B325:B326"/>
     <mergeCell ref="C325:C326"/>
+    <mergeCell ref="D325:D326"/>
     <mergeCell ref="A327:A329"/>
     <mergeCell ref="B327:B329"/>
     <mergeCell ref="C327:C329"/>
+    <mergeCell ref="D327:D329"/>
     <mergeCell ref="A333:A335"/>
     <mergeCell ref="B333:B335"/>
     <mergeCell ref="C333:C335"/>
+    <mergeCell ref="D333:D335"/>
     <mergeCell ref="A338:A339"/>
     <mergeCell ref="B338:B339"/>
     <mergeCell ref="C338:C339"/>
+    <mergeCell ref="D338:D339"/>
     <mergeCell ref="A340:A341"/>
     <mergeCell ref="B340:B341"/>
     <mergeCell ref="C340:C341"/>
+    <mergeCell ref="D340:D341"/>
     <mergeCell ref="A342:A343"/>
     <mergeCell ref="B342:B343"/>
     <mergeCell ref="C342:C343"/>
+    <mergeCell ref="D342:D343"/>
     <mergeCell ref="A344:A350"/>
     <mergeCell ref="B344:B350"/>
     <mergeCell ref="C344:C350"/>
+    <mergeCell ref="D344:D350"/>
     <mergeCell ref="A351:A352"/>
     <mergeCell ref="B351:B352"/>
     <mergeCell ref="C351:C352"/>
+    <mergeCell ref="D351:D352"/>
     <mergeCell ref="A353:A354"/>
     <mergeCell ref="B353:B354"/>
     <mergeCell ref="C353:C354"/>
+    <mergeCell ref="D353:D354"/>
     <mergeCell ref="A355:A358"/>
     <mergeCell ref="B355:B358"/>
     <mergeCell ref="C355:C358"/>
+    <mergeCell ref="D355:D358"/>
     <mergeCell ref="A359:A362"/>
     <mergeCell ref="B359:B362"/>
     <mergeCell ref="C359:C362"/>
+    <mergeCell ref="D359:D362"/>
     <mergeCell ref="A364:A367"/>
     <mergeCell ref="B364:B367"/>
     <mergeCell ref="C364:C367"/>
+    <mergeCell ref="D364:D367"/>
     <mergeCell ref="A369:A373"/>
     <mergeCell ref="B369:B373"/>
     <mergeCell ref="C369:C373"/>
+    <mergeCell ref="D369:D373"/>
     <mergeCell ref="A375:A377"/>
     <mergeCell ref="B375:B377"/>
     <mergeCell ref="C375:C377"/>
+    <mergeCell ref="D375:D377"/>
     <mergeCell ref="A379:A380"/>
     <mergeCell ref="B379:B380"/>
     <mergeCell ref="C379:C380"/>
+    <mergeCell ref="D379:D380"/>
     <mergeCell ref="A381:A383"/>
     <mergeCell ref="B381:B383"/>
     <mergeCell ref="C381:C383"/>
+    <mergeCell ref="D381:D383"/>
     <mergeCell ref="A385:A386"/>
     <mergeCell ref="B385:B386"/>
     <mergeCell ref="C385:C386"/>
+    <mergeCell ref="D385:D386"/>
     <mergeCell ref="A387:A399"/>
     <mergeCell ref="B387:B399"/>
     <mergeCell ref="C387:C399"/>
+    <mergeCell ref="D387:D399"/>
     <mergeCell ref="A404:A409"/>
     <mergeCell ref="B404:B409"/>
     <mergeCell ref="C404:C409"/>
+    <mergeCell ref="D404:D409"/>
     <mergeCell ref="A411:A417"/>
     <mergeCell ref="B411:B417"/>
     <mergeCell ref="C411:C417"/>
+    <mergeCell ref="D411:D417"/>
     <mergeCell ref="A422:A424"/>
     <mergeCell ref="B422:B424"/>
     <mergeCell ref="C422:C424"/>
+    <mergeCell ref="D422:D424"/>
     <mergeCell ref="A426:A430"/>
     <mergeCell ref="B426:B430"/>
     <mergeCell ref="C426:C430"/>
+    <mergeCell ref="D426:D430"/>
     <mergeCell ref="A434:A440"/>
     <mergeCell ref="B434:B440"/>
     <mergeCell ref="C434:C440"/>
+    <mergeCell ref="D434:D440"/>
     <mergeCell ref="A442:A446"/>
     <mergeCell ref="B442:B446"/>
     <mergeCell ref="C442:C446"/>
+    <mergeCell ref="D442:D446"/>
     <mergeCell ref="A449:A452"/>
     <mergeCell ref="B449:B452"/>
     <mergeCell ref="C449:C452"/>
+    <mergeCell ref="D449:D452"/>
   </mergeCells>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
